--- a/Modelos/Entrada_DM.xlsx
+++ b/Modelos/Entrada_DM.xlsx
@@ -100,7 +100,7 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Grupo usado na média do VPLBc (linhas com o mesmo nome são agregadas)</t>
+          <t xml:space="preserve">Sim = entra no DM médio do componente; Não = fica de fora</t>
         </r>
       </text>
     </comment>
@@ -112,7 +112,7 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Sim = entra na média do VPLBc do grupo; Não = fica de fora</t>
+          <t xml:space="preserve">Medida do atributo antes do impacto (M_pre)</t>
         </r>
       </text>
     </comment>
@@ -124,7 +124,7 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Medida do atributo antes do impacto (M_pre)</t>
+          <t xml:space="preserve">Medida do atributo depois do impacto (M_pos)</t>
         </r>
       </text>
     </comment>
@@ -136,7 +136,7 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Medida do atributo depois do impacto (M_pos)</t>
+          <t xml:space="preserve">Valor de referência do atributo no local do impacto (Bi), &gt; 0</t>
         </r>
       </text>
     </comment>
@@ -148,7 +148,7 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Valor de referência do atributo no local do impacto (Bi), &gt; 0</t>
+          <t xml:space="preserve">Área do impacto (a), em hectares</t>
         </r>
       </text>
     </comment>
@@ -160,7 +160,7 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Área do impacto (a), em hectares</t>
+          <t xml:space="preserve">Medida do atributo antes da compensação (M_pre)</t>
         </r>
       </text>
     </comment>
@@ -172,7 +172,7 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Medida do atributo antes da compensação (M_pre)</t>
+          <t xml:space="preserve">Medida do atributo depois da compensação (M_pos)</t>
         </r>
       </text>
     </comment>
@@ -184,7 +184,7 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Medida do atributo depois da compensação (M_pos)</t>
+          <t xml:space="preserve">Valor de referência do atributo no local da compensação (Bi), &gt; 0</t>
         </r>
       </text>
     </comment>
@@ -196,55 +196,7 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Valor de referência do atributo no local da compensação (Bi), &gt; 0</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
           <t xml:space="preserve">Área da compensação (a), em hectares</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">Taxa de desconto no tempo (d). Vazio = valor da aba Parametros</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="R1" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">Taxa de incerteza da compensação (y): 0,62 / 0,825 / 0,955. Vazio = aba Parametros</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <name val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">Tempo (t), em anos. Vazio = valor da aba Parametros</t>
         </r>
       </text>
     </comment>
@@ -253,7 +205,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
     <t xml:space="preserve">Planilha de entrada para R/DM-Calculo_Perdas_Ganhos.R</t>
   </si>
@@ -267,10 +219,10 @@
     <t xml:space="preserve">Não renomeie as colunas da linha 1 da aba 'Entrada' (o script lê os nomes).</t>
   </si>
   <si>
-    <t xml:space="preserve">A aba 'Parametros' guarda os valores padrão de d, y e t, usados quando a linha deixa d, y ou t vazios.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use ponto ou vírgula como separador decimal; números digitados como texto também são aceitos.</t>
+    <t xml:space="preserve">A aba 'Parametros' guarda os valores de d, y e t, usados em todas as linhas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digite os valores das colunas M, Bi e a como número (não como texto).</t>
   </si>
   <si>
     <t xml:space="preserve">As linhas de exemplo são os dados da aba 'Aplicação DM' do Gabarito_DM.xlsx.</t>
@@ -345,16 +297,10 @@
     <t xml:space="preserve">E</t>
   </si>
   <si>
-    <t xml:space="preserve">grupo_vplbc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grupo usado na média do VPLBc (linhas com o mesmo nome são agregadas)</t>
-  </si>
-  <si>
     <t xml:space="preserve">incluir_vplbc</t>
   </si>
   <si>
-    <t xml:space="preserve">Sim = entra na média do VPLBc do grupo; Não = fica de fora</t>
+    <t xml:space="preserve">Sim = entra no DM médio do componente; Não = fica de fora</t>
   </si>
   <si>
     <t xml:space="preserve">M_pre_imp</t>
@@ -429,166 +375,124 @@
     <t xml:space="preserve">AB</t>
   </si>
   <si>
+    <t xml:space="preserve">Palmito Jussara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamanho da população de Palmito Juçara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Número de indivíduos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euterpe edulis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portal CNCFlora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espécies ameaçadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diversidade de espécies ameaçadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riqueza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espécies endêmicas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamanho da população de Guapuruvu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schizolobium parahyba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMBRAPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diversidade de espécies endêmicas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabarelli &amp; Mantovani 1999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floresta Ombrófila Densa de Mata Atlântica Terras baixas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicadora de estágio maduro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cupania oblongifolia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baitello et al. 1992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicadora de estágio inicial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abundância</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forma de vida arbórea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espécies arbóreas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campos et al. 2011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polinização Zoofílica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espécies zoófilas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colonetti et al. 2009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Número de indivíduos de Guapuruvu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espécies Zoófilas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iamara-Nogueira et al. 2021; Boscolo et al. 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoocoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espécies Zoocóricas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miranda et al. 2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piña-Rodrigues 1997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parametro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valor</t>
+  </si>
+  <si>
     <t xml:space="preserve">d</t>
   </si>
   <si>
-    <t xml:space="preserve">Taxa de desconto no tempo (d). Vazio = valor da aba Parametros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AD</t>
+    <t xml:space="preserve">Taxa de desconto no tempo (ex.: 0,03 = 3% ao ano)</t>
   </si>
   <si>
     <t xml:space="preserve">y</t>
   </si>
   <si>
-    <t xml:space="preserve">Taxa de incerteza da compensação (y): 0,62 / 0,825 / 0,955. Vazio = aba Parametros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AE</t>
+    <t xml:space="preserve">Taxa de incerteza: 0,62 (baixa), 0,825 (média), 0,955 (alta)</t>
   </si>
   <si>
     <t xml:space="preserve">t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tempo (t), em anos. Vazio = valor da aba Parametros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palmito Jussara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tamanho da população de Palmito Juçara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de indivíduos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Euterpe edulis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal CNCFlora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palmito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Espécies ameaçadas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diversidade de espécies ameaçadas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riqueza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ameaçadas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Espécies endêmicas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tamanho da população de Guapuruvu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schizolobium parahyba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMBRAPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guapuruvu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diversidade de espécies endêmicas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tabarelli &amp; Mantovani 1999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endêmicas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Floresta Ombrófila Densa de Mata Atlântica Terras baixas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indicadora de estágio maduro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cupania oblongifolia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baitello et al. 1992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estágio maduro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indicadora de estágio inicial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abundância</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estágio inicial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forma de vida arbórea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Espécies arbóreas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campos et al. 2011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arbórea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polinização Zoofílica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Espécies zoófilas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colonetti et al. 2009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polinização</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de indivíduos de Guapuruvu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Espécies Zoófilas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iamara-Nogueira et al. 2021; Boscolo et al. 2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zoocoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Espécies Zoocóricas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miranda et al. 2019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piña-Rodrigues 1997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parametro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taxa de desconto no tempo (ex.: 0,03 = 3% ao ano)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taxa de incerteza: 0,62 (baixa), 0,825 (média), 0,955 (alta)</t>
   </si>
   <si>
     <t xml:space="preserve">Tempo, em anos, até a compensação atingir nenhuma perda líquida</t>
@@ -1134,161 +1038,105 @@
         <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B22" t="s">
         <v>12</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
         <v>55</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" t="s">
-        <v>59</v>
-      </c>
-      <c r="D26" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>64</v>
-      </c>
-      <c r="B28" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1308,8 +1156,8 @@
     <col min="4" max="4" width="28.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="26.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="30.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="13.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="13.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="11.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="11.71" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="11.71" hidden="0" customWidth="1"/>
@@ -1317,10 +1165,6 @@
     <col min="13" max="13" width="11.71" hidden="0" customWidth="1"/>
     <col min="14" max="14" width="11.71" hidden="0" customWidth="1"/>
     <col min="15" max="15" width="11.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="11.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="11.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="11.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="11.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1349,37 +1193,25 @@
         <v>32</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2">
@@ -1387,58 +1219,46 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H2" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>0.0317487106298096</v>
+      </c>
+      <c r="L2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="M2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="N2" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="L2" s="4" t="n">
-        <v>0.0317487106298096</v>
-      </c>
-      <c r="M2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="4" t="n">
-        <v>6</v>
-      </c>
       <c r="O2" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="P2" s="4" t="n">
         <v>10.7439</v>
-      </c>
-      <c r="Q2" s="4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="R2" s="4" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="S2" s="4" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -1446,56 +1266,44 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H3" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>0.0317487106298096</v>
+      </c>
+      <c r="L3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="M3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="L3" s="4" t="n">
-        <v>0.0317487106298096</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="O3" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="P3" s="4" t="n">
         <v>10.7439</v>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="R3" s="4" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -1503,58 +1311,46 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H4" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>0.0317487106298096</v>
+      </c>
+      <c r="L4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="M4" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="N4" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="L4" s="4" t="n">
-        <v>0.0317487106298096</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>26</v>
-      </c>
       <c r="O4" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="P4" s="4" t="n">
         <v>10.7439</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -1562,58 +1358,46 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H5" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="H5" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="I5" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0.0317487106298096</v>
+      </c>
+      <c r="L5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="M5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="L5" s="4" t="n">
-        <v>0.0317487106298096</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="O5" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="P5" s="4" t="n">
         <v>10.7439</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -1621,58 +1405,46 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H6" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0.0317487106298096</v>
+      </c>
+      <c r="L6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="M6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="L6" s="4" t="n">
-        <v>0.0317487106298096</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="O6" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="P6" s="4" t="n">
         <v>10.7439</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -1680,56 +1452,44 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H7" s="3" t="s">
         <v>24</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>6</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>6</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K7" s="4" t="n">
+        <v>0.0317487106298096</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="N7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="L7" s="4" t="n">
-        <v>0.0317487106298096</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>26</v>
-      </c>
       <c r="O7" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="P7" s="4" t="n">
         <v>10.7439</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="R7" s="4" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="S7" s="4" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1737,58 +1497,46 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H8" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="H8" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="I8" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="n">
+        <v>142</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0.0317487106298096</v>
+      </c>
+      <c r="L8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="M8" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="N8" s="4" t="n">
         <v>142</v>
       </c>
-      <c r="L8" s="4" t="n">
-        <v>0.0317487106298096</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>31</v>
-      </c>
       <c r="O8" s="4" t="n">
-        <v>142</v>
-      </c>
-      <c r="P8" s="4" t="n">
         <v>10.7439</v>
-      </c>
-      <c r="Q8" s="4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="R8" s="4" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="S8" s="4" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -1796,58 +1544,46 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H9" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="H9" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="I9" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J9" s="4" t="n">
+        <v>1274</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0.0317487106298096</v>
+      </c>
+      <c r="L9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="M9" s="4" t="n">
+        <v>821</v>
+      </c>
+      <c r="N9" s="4" t="n">
         <v>1274</v>
       </c>
-      <c r="L9" s="4" t="n">
-        <v>0.0317487106298096</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>821</v>
-      </c>
       <c r="O9" s="4" t="n">
-        <v>1274</v>
-      </c>
-      <c r="P9" s="4" t="n">
         <v>10.7439</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -1855,58 +1591,46 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="4" t="n">
+      <c r="K10" s="4" t="n">
+        <v>0.0317487106298096</v>
+      </c>
+      <c r="L10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="4" t="n">
+      <c r="M10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="N10" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="L10" s="4" t="n">
-        <v>0.0317487106298096</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>7</v>
-      </c>
       <c r="O10" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="P10" s="4" t="n">
         <v>10.7439</v>
-      </c>
-      <c r="Q10" s="4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="R10" s="4" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="S10" s="4" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -1914,58 +1638,46 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="H11" s="3" t="s">
         <v>24</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>6</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>6</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="K11" s="4" t="n">
+        <v>0.0317487106298096</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="N11" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="L11" s="4" t="n">
-        <v>0.0317487106298096</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>26</v>
-      </c>
       <c r="O11" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="P11" s="4" t="n">
         <v>10.7439</v>
-      </c>
-      <c r="Q11" s="4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="R11" s="4" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="S11" s="4" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -1973,58 +1685,46 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="H12" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="H12" s="4" t="n">
+        <v>12</v>
+      </c>
       <c r="I12" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J12" s="4" t="n">
+        <v>1715</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0.0317487106298096</v>
+      </c>
+      <c r="L12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="4" t="n">
+      <c r="M12" s="4" t="n">
+        <v>342</v>
+      </c>
+      <c r="N12" s="4" t="n">
         <v>1715</v>
       </c>
-      <c r="L12" s="4" t="n">
-        <v>0.0317487106298096</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>342</v>
-      </c>
       <c r="O12" s="4" t="n">
-        <v>1715</v>
-      </c>
-      <c r="P12" s="4" t="n">
         <v>10.7439</v>
-      </c>
-      <c r="Q12" s="4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="R12" s="4" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="S12" s="4" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -2032,58 +1732,46 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="D13" s="3" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H13" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="H13" s="4" t="n">
+        <v>13</v>
+      </c>
       <c r="I13" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0.0317487106298096</v>
+      </c>
+      <c r="L13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="4" t="n">
+      <c r="M13" s="4" t="n">
+        <v>565</v>
+      </c>
+      <c r="N13" s="4" t="n">
         <v>1600</v>
       </c>
-      <c r="L13" s="4" t="n">
-        <v>0.0317487106298096</v>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v>565</v>
-      </c>
       <c r="O13" s="4" t="n">
-        <v>1600</v>
-      </c>
-      <c r="P13" s="4" t="n">
         <v>10.7439</v>
-      </c>
-      <c r="Q13" s="4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="R13" s="4" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="S13" s="4" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -2091,58 +1779,46 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="D14" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H14" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="H14" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="I14" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0.0317487106298096</v>
+      </c>
+      <c r="L14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="4" t="n">
+      <c r="M14" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="N14" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="L14" s="4" t="n">
-        <v>0.0317487106298096</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v>18</v>
-      </c>
       <c r="O14" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="P14" s="4" t="n">
         <v>10.7439</v>
-      </c>
-      <c r="Q14" s="4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="R14" s="4" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="S14" s="4" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -2153,7 +1829,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
@@ -2161,10 +1837,6 @@
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
     </row>
     <row r="16">
       <c r="A16" s="3"/>
@@ -2174,7 +1846,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+      <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
@@ -2182,10 +1854,6 @@
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
     </row>
     <row r="17">
       <c r="A17" s="3"/>
@@ -2195,7 +1863,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+      <c r="H17" s="4"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
@@ -2203,10 +1871,6 @@
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
     </row>
     <row r="18">
       <c r="A18" s="3"/>
@@ -2216,7 +1880,7 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+      <c r="H18" s="4"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
@@ -2224,10 +1888,6 @@
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="4"/>
-      <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
     </row>
     <row r="19">
       <c r="A19" s="3"/>
@@ -2237,7 +1897,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+      <c r="H19" s="4"/>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
@@ -2245,10 +1905,6 @@
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
     </row>
     <row r="20">
       <c r="A20" s="3"/>
@@ -2258,7 +1914,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
+      <c r="H20" s="4"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
@@ -2266,10 +1922,6 @@
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="4"/>
-      <c r="S20" s="4"/>
     </row>
     <row r="21">
       <c r="A21" s="3"/>
@@ -2279,7 +1931,7 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
+      <c r="H21" s="4"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
@@ -2287,10 +1939,6 @@
       <c r="M21" s="4"/>
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4"/>
-      <c r="S21" s="4"/>
     </row>
     <row r="22">
       <c r="A22" s="3"/>
@@ -2300,7 +1948,7 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+      <c r="H22" s="4"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
@@ -2308,10 +1956,6 @@
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="4"/>
-      <c r="S22" s="4"/>
     </row>
     <row r="23">
       <c r="A23" s="3"/>
@@ -2321,7 +1965,7 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
+      <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
@@ -2329,10 +1973,6 @@
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="4"/>
-      <c r="S23" s="4"/>
     </row>
     <row r="24">
       <c r="A24" s="3"/>
@@ -2342,7 +1982,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
+      <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
@@ -2350,10 +1990,6 @@
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="4"/>
-      <c r="S24" s="4"/>
     </row>
     <row r="25">
       <c r="A25" s="3"/>
@@ -2363,7 +1999,7 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
+      <c r="H25" s="4"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
@@ -2371,10 +2007,6 @@
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
       <c r="O25" s="4"/>
-      <c r="P25" s="4"/>
-      <c r="Q25" s="4"/>
-      <c r="R25" s="4"/>
-      <c r="S25" s="4"/>
     </row>
     <row r="26">
       <c r="A26" s="3"/>
@@ -2384,7 +2016,7 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
+      <c r="H26" s="4"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
@@ -2392,10 +2024,6 @@
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
       <c r="O26" s="4"/>
-      <c r="P26" s="4"/>
-      <c r="Q26" s="4"/>
-      <c r="R26" s="4"/>
-      <c r="S26" s="4"/>
     </row>
     <row r="27">
       <c r="A27" s="3"/>
@@ -2405,7 +2033,7 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
+      <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
@@ -2413,10 +2041,6 @@
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
       <c r="O27" s="4"/>
-      <c r="P27" s="4"/>
-      <c r="Q27" s="4"/>
-      <c r="R27" s="4"/>
-      <c r="S27" s="4"/>
     </row>
     <row r="28">
       <c r="A28" s="3"/>
@@ -2426,7 +2050,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
+      <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
@@ -2434,10 +2058,6 @@
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>
       <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="4"/>
-      <c r="S28" s="4"/>
     </row>
     <row r="29">
       <c r="A29" s="3"/>
@@ -2447,7 +2067,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
+      <c r="H29" s="4"/>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
@@ -2455,10 +2075,6 @@
       <c r="M29" s="4"/>
       <c r="N29" s="4"/>
       <c r="O29" s="4"/>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="4"/>
-      <c r="S29" s="4"/>
     </row>
     <row r="30">
       <c r="A30" s="3"/>
@@ -2468,7 +2084,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
+      <c r="H30" s="4"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
@@ -2476,10 +2092,6 @@
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
       <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="4"/>
-      <c r="S30" s="4"/>
     </row>
     <row r="31">
       <c r="A31" s="3"/>
@@ -2489,7 +2101,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
+      <c r="H31" s="4"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
@@ -2497,10 +2109,6 @@
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
       <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="4"/>
-      <c r="S31" s="4"/>
     </row>
     <row r="32">
       <c r="A32" s="3"/>
@@ -2510,7 +2118,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
+      <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
@@ -2518,10 +2126,6 @@
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
-      <c r="R32" s="4"/>
-      <c r="S32" s="4"/>
     </row>
     <row r="33">
       <c r="A33" s="3"/>
@@ -2531,7 +2135,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
+      <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
@@ -2539,10 +2143,6 @@
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
-      <c r="R33" s="4"/>
-      <c r="S33" s="4"/>
     </row>
     <row r="34">
       <c r="A34" s="3"/>
@@ -2552,7 +2152,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
+      <c r="H34" s="4"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
@@ -2560,10 +2160,6 @@
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
-      <c r="R34" s="4"/>
-      <c r="S34" s="4"/>
     </row>
     <row r="35">
       <c r="A35" s="3"/>
@@ -2573,7 +2169,7 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
+      <c r="H35" s="4"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
@@ -2581,10 +2177,6 @@
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="4"/>
-      <c r="S35" s="4"/>
     </row>
     <row r="36">
       <c r="A36" s="3"/>
@@ -2594,7 +2186,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
+      <c r="H36" s="4"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
@@ -2602,10 +2194,6 @@
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
     </row>
     <row r="37">
       <c r="A37" s="3"/>
@@ -2615,7 +2203,7 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
+      <c r="H37" s="4"/>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
@@ -2623,10 +2211,6 @@
       <c r="M37" s="4"/>
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
-      <c r="Q37" s="4"/>
-      <c r="R37" s="4"/>
-      <c r="S37" s="4"/>
     </row>
     <row r="38">
       <c r="A38" s="3"/>
@@ -2636,7 +2220,7 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
+      <c r="H38" s="4"/>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
@@ -2644,10 +2228,6 @@
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="4"/>
-      <c r="R38" s="4"/>
-      <c r="S38" s="4"/>
     </row>
     <row r="39">
       <c r="A39" s="3"/>
@@ -2657,7 +2237,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
+      <c r="H39" s="4"/>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
@@ -2665,10 +2245,6 @@
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
-      <c r="P39" s="4"/>
-      <c r="Q39" s="4"/>
-      <c r="R39" s="4"/>
-      <c r="S39" s="4"/>
     </row>
     <row r="40">
       <c r="A40" s="3"/>
@@ -2678,7 +2254,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
+      <c r="H40" s="4"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
@@ -2686,10 +2262,6 @@
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
-      <c r="P40" s="4"/>
-      <c r="Q40" s="4"/>
-      <c r="R40" s="4"/>
-      <c r="S40" s="4"/>
     </row>
     <row r="41">
       <c r="A41" s="3"/>
@@ -2699,7 +2271,7 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
+      <c r="H41" s="4"/>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
@@ -2707,10 +2279,6 @@
       <c r="M41" s="4"/>
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
-      <c r="P41" s="4"/>
-      <c r="Q41" s="4"/>
-      <c r="R41" s="4"/>
-      <c r="S41" s="4"/>
     </row>
     <row r="42">
       <c r="A42" s="3"/>
@@ -2720,7 +2288,7 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
+      <c r="H42" s="4"/>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
@@ -2728,10 +2296,6 @@
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
-      <c r="P42" s="4"/>
-      <c r="Q42" s="4"/>
-      <c r="R42" s="4"/>
-      <c r="S42" s="4"/>
     </row>
     <row r="43">
       <c r="A43" s="3"/>
@@ -2741,7 +2305,7 @@
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
+      <c r="H43" s="4"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
@@ -2749,10 +2313,6 @@
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
-      <c r="P43" s="4"/>
-      <c r="Q43" s="4"/>
-      <c r="R43" s="4"/>
-      <c r="S43" s="4"/>
     </row>
     <row r="44">
       <c r="A44" s="3"/>
@@ -2762,7 +2322,7 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
+      <c r="H44" s="4"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
@@ -2770,10 +2330,6 @@
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
-      <c r="P44" s="4"/>
-      <c r="Q44" s="4"/>
-      <c r="R44" s="4"/>
-      <c r="S44" s="4"/>
     </row>
     <row r="45">
       <c r="A45" s="3"/>
@@ -2783,7 +2339,7 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
+      <c r="H45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
@@ -2791,10 +2347,6 @@
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
-      <c r="P45" s="4"/>
-      <c r="Q45" s="4"/>
-      <c r="R45" s="4"/>
-      <c r="S45" s="4"/>
     </row>
     <row r="46">
       <c r="A46" s="3"/>
@@ -2804,7 +2356,7 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
+      <c r="H46" s="4"/>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
@@ -2812,10 +2364,6 @@
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
-      <c r="P46" s="4"/>
-      <c r="Q46" s="4"/>
-      <c r="R46" s="4"/>
-      <c r="S46" s="4"/>
     </row>
     <row r="47">
       <c r="A47" s="3"/>
@@ -2825,7 +2373,7 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
+      <c r="H47" s="4"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
@@ -2833,10 +2381,6 @@
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
-      <c r="P47" s="4"/>
-      <c r="Q47" s="4"/>
-      <c r="R47" s="4"/>
-      <c r="S47" s="4"/>
     </row>
     <row r="48">
       <c r="A48" s="3"/>
@@ -2846,7 +2390,7 @@
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
+      <c r="H48" s="4"/>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
@@ -2854,10 +2398,6 @@
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
-      <c r="P48" s="4"/>
-      <c r="Q48" s="4"/>
-      <c r="R48" s="4"/>
-      <c r="S48" s="4"/>
     </row>
     <row r="49">
       <c r="A49" s="3"/>
@@ -2867,7 +2407,7 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
+      <c r="H49" s="4"/>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
       <c r="K49" s="4"/>
@@ -2875,10 +2415,6 @@
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
-      <c r="P49" s="4"/>
-      <c r="Q49" s="4"/>
-      <c r="R49" s="4"/>
-      <c r="S49" s="4"/>
     </row>
     <row r="50">
       <c r="A50" s="3"/>
@@ -2888,7 +2424,7 @@
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
+      <c r="H50" s="4"/>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
@@ -2896,10 +2432,6 @@
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
-      <c r="P50" s="4"/>
-      <c r="Q50" s="4"/>
-      <c r="R50" s="4"/>
-      <c r="S50" s="4"/>
     </row>
     <row r="51">
       <c r="A51" s="3"/>
@@ -2909,7 +2441,7 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
+      <c r="H51" s="4"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
       <c r="K51" s="4"/>
@@ -2917,10 +2449,6 @@
       <c r="M51" s="4"/>
       <c r="N51" s="4"/>
       <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="4"/>
-      <c r="S51" s="4"/>
     </row>
     <row r="52">
       <c r="A52" s="3"/>
@@ -2930,7 +2458,7 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
+      <c r="H52" s="4"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>
@@ -2938,10 +2466,6 @@
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
-      <c r="P52" s="4"/>
-      <c r="Q52" s="4"/>
-      <c r="R52" s="4"/>
-      <c r="S52" s="4"/>
     </row>
     <row r="53">
       <c r="A53" s="3"/>
@@ -2951,7 +2475,7 @@
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
+      <c r="H53" s="4"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
       <c r="K53" s="4"/>
@@ -2959,10 +2483,6 @@
       <c r="M53" s="4"/>
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
-      <c r="P53" s="4"/>
-      <c r="Q53" s="4"/>
-      <c r="R53" s="4"/>
-      <c r="S53" s="4"/>
     </row>
     <row r="54">
       <c r="A54" s="3"/>
@@ -2972,7 +2492,7 @@
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
+      <c r="H54" s="4"/>
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
       <c r="K54" s="4"/>
@@ -2980,10 +2500,6 @@
       <c r="M54" s="4"/>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
-      <c r="P54" s="4"/>
-      <c r="Q54" s="4"/>
-      <c r="R54" s="4"/>
-      <c r="S54" s="4"/>
     </row>
     <row r="55">
       <c r="A55" s="3"/>
@@ -2993,7 +2509,7 @@
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
+      <c r="H55" s="4"/>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
       <c r="K55" s="4"/>
@@ -3001,10 +2517,6 @@
       <c r="M55" s="4"/>
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
-      <c r="P55" s="4"/>
-      <c r="Q55" s="4"/>
-      <c r="R55" s="4"/>
-      <c r="S55" s="4"/>
     </row>
     <row r="56">
       <c r="A56" s="3"/>
@@ -3014,7 +2526,7 @@
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
+      <c r="H56" s="4"/>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
       <c r="K56" s="4"/>
@@ -3022,10 +2534,6 @@
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
-      <c r="P56" s="4"/>
-      <c r="Q56" s="4"/>
-      <c r="R56" s="4"/>
-      <c r="S56" s="4"/>
     </row>
     <row r="57">
       <c r="A57" s="3"/>
@@ -3035,7 +2543,7 @@
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
+      <c r="H57" s="4"/>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
       <c r="K57" s="4"/>
@@ -3043,10 +2551,6 @@
       <c r="M57" s="4"/>
       <c r="N57" s="4"/>
       <c r="O57" s="4"/>
-      <c r="P57" s="4"/>
-      <c r="Q57" s="4"/>
-      <c r="R57" s="4"/>
-      <c r="S57" s="4"/>
     </row>
     <row r="58">
       <c r="A58" s="3"/>
@@ -3056,7 +2560,7 @@
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
+      <c r="H58" s="4"/>
       <c r="I58" s="4"/>
       <c r="J58" s="4"/>
       <c r="K58" s="4"/>
@@ -3064,10 +2568,6 @@
       <c r="M58" s="4"/>
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
-      <c r="P58" s="4"/>
-      <c r="Q58" s="4"/>
-      <c r="R58" s="4"/>
-      <c r="S58" s="4"/>
     </row>
     <row r="59">
       <c r="A59" s="3"/>
@@ -3077,7 +2577,7 @@
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
+      <c r="H59" s="4"/>
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
       <c r="K59" s="4"/>
@@ -3085,10 +2585,6 @@
       <c r="M59" s="4"/>
       <c r="N59" s="4"/>
       <c r="O59" s="4"/>
-      <c r="P59" s="4"/>
-      <c r="Q59" s="4"/>
-      <c r="R59" s="4"/>
-      <c r="S59" s="4"/>
     </row>
     <row r="60">
       <c r="A60" s="3"/>
@@ -3098,7 +2594,7 @@
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
+      <c r="H60" s="4"/>
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
       <c r="K60" s="4"/>
@@ -3106,10 +2602,6 @@
       <c r="M60" s="4"/>
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
-      <c r="P60" s="4"/>
-      <c r="Q60" s="4"/>
-      <c r="R60" s="4"/>
-      <c r="S60" s="4"/>
     </row>
     <row r="61">
       <c r="A61" s="3"/>
@@ -3119,7 +2611,7 @@
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
+      <c r="H61" s="4"/>
       <c r="I61" s="4"/>
       <c r="J61" s="4"/>
       <c r="K61" s="4"/>
@@ -3127,10 +2619,6 @@
       <c r="M61" s="4"/>
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
-      <c r="P61" s="4"/>
-      <c r="Q61" s="4"/>
-      <c r="R61" s="4"/>
-      <c r="S61" s="4"/>
     </row>
     <row r="62">
       <c r="A62" s="3"/>
@@ -3140,7 +2628,7 @@
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
+      <c r="H62" s="4"/>
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
       <c r="K62" s="4"/>
@@ -3148,10 +2636,6 @@
       <c r="M62" s="4"/>
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
-      <c r="P62" s="4"/>
-      <c r="Q62" s="4"/>
-      <c r="R62" s="4"/>
-      <c r="S62" s="4"/>
     </row>
     <row r="63">
       <c r="A63" s="3"/>
@@ -3161,7 +2645,7 @@
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
+      <c r="H63" s="4"/>
       <c r="I63" s="4"/>
       <c r="J63" s="4"/>
       <c r="K63" s="4"/>
@@ -3169,10 +2653,6 @@
       <c r="M63" s="4"/>
       <c r="N63" s="4"/>
       <c r="O63" s="4"/>
-      <c r="P63" s="4"/>
-      <c r="Q63" s="4"/>
-      <c r="R63" s="4"/>
-      <c r="S63" s="4"/>
     </row>
     <row r="64">
       <c r="A64" s="3"/>
@@ -3182,7 +2662,7 @@
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
+      <c r="H64" s="4"/>
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
       <c r="K64" s="4"/>
@@ -3190,10 +2670,6 @@
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
-      <c r="P64" s="4"/>
-      <c r="Q64" s="4"/>
-      <c r="R64" s="4"/>
-      <c r="S64" s="4"/>
     </row>
     <row r="65">
       <c r="A65" s="3"/>
@@ -3203,7 +2679,7 @@
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
+      <c r="H65" s="4"/>
       <c r="I65" s="4"/>
       <c r="J65" s="4"/>
       <c r="K65" s="4"/>
@@ -3211,10 +2687,6 @@
       <c r="M65" s="4"/>
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
-      <c r="P65" s="4"/>
-      <c r="Q65" s="4"/>
-      <c r="R65" s="4"/>
-      <c r="S65" s="4"/>
     </row>
     <row r="66">
       <c r="A66" s="3"/>
@@ -3224,7 +2696,7 @@
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
+      <c r="H66" s="4"/>
       <c r="I66" s="4"/>
       <c r="J66" s="4"/>
       <c r="K66" s="4"/>
@@ -3232,10 +2704,6 @@
       <c r="M66" s="4"/>
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
-      <c r="P66" s="4"/>
-      <c r="Q66" s="4"/>
-      <c r="R66" s="4"/>
-      <c r="S66" s="4"/>
     </row>
     <row r="67">
       <c r="A67" s="3"/>
@@ -3245,7 +2713,7 @@
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
+      <c r="H67" s="4"/>
       <c r="I67" s="4"/>
       <c r="J67" s="4"/>
       <c r="K67" s="4"/>
@@ -3253,10 +2721,6 @@
       <c r="M67" s="4"/>
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
-      <c r="P67" s="4"/>
-      <c r="Q67" s="4"/>
-      <c r="R67" s="4"/>
-      <c r="S67" s="4"/>
     </row>
     <row r="68">
       <c r="A68" s="3"/>
@@ -3266,7 +2730,7 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
+      <c r="H68" s="4"/>
       <c r="I68" s="4"/>
       <c r="J68" s="4"/>
       <c r="K68" s="4"/>
@@ -3274,10 +2738,6 @@
       <c r="M68" s="4"/>
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
-      <c r="P68" s="4"/>
-      <c r="Q68" s="4"/>
-      <c r="R68" s="4"/>
-      <c r="S68" s="4"/>
     </row>
     <row r="69">
       <c r="A69" s="3"/>
@@ -3287,7 +2747,7 @@
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
+      <c r="H69" s="4"/>
       <c r="I69" s="4"/>
       <c r="J69" s="4"/>
       <c r="K69" s="4"/>
@@ -3295,10 +2755,6 @@
       <c r="M69" s="4"/>
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
-      <c r="P69" s="4"/>
-      <c r="Q69" s="4"/>
-      <c r="R69" s="4"/>
-      <c r="S69" s="4"/>
     </row>
     <row r="70">
       <c r="A70" s="3"/>
@@ -3308,7 +2764,7 @@
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
+      <c r="H70" s="4"/>
       <c r="I70" s="4"/>
       <c r="J70" s="4"/>
       <c r="K70" s="4"/>
@@ -3316,10 +2772,6 @@
       <c r="M70" s="4"/>
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
-      <c r="P70" s="4"/>
-      <c r="Q70" s="4"/>
-      <c r="R70" s="4"/>
-      <c r="S70" s="4"/>
     </row>
     <row r="71">
       <c r="A71" s="3"/>
@@ -3329,7 +2781,7 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
+      <c r="H71" s="4"/>
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
       <c r="K71" s="4"/>
@@ -3337,10 +2789,6 @@
       <c r="M71" s="4"/>
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
-      <c r="P71" s="4"/>
-      <c r="Q71" s="4"/>
-      <c r="R71" s="4"/>
-      <c r="S71" s="4"/>
     </row>
     <row r="72">
       <c r="A72" s="3"/>
@@ -3350,7 +2798,7 @@
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
+      <c r="H72" s="4"/>
       <c r="I72" s="4"/>
       <c r="J72" s="4"/>
       <c r="K72" s="4"/>
@@ -3358,10 +2806,6 @@
       <c r="M72" s="4"/>
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
-      <c r="P72" s="4"/>
-      <c r="Q72" s="4"/>
-      <c r="R72" s="4"/>
-      <c r="S72" s="4"/>
     </row>
     <row r="73">
       <c r="A73" s="3"/>
@@ -3371,7 +2815,7 @@
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
+      <c r="H73" s="4"/>
       <c r="I73" s="4"/>
       <c r="J73" s="4"/>
       <c r="K73" s="4"/>
@@ -3379,10 +2823,6 @@
       <c r="M73" s="4"/>
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
-      <c r="P73" s="4"/>
-      <c r="Q73" s="4"/>
-      <c r="R73" s="4"/>
-      <c r="S73" s="4"/>
     </row>
     <row r="74">
       <c r="A74" s="3"/>
@@ -3392,7 +2832,7 @@
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
+      <c r="H74" s="4"/>
       <c r="I74" s="4"/>
       <c r="J74" s="4"/>
       <c r="K74" s="4"/>
@@ -3400,10 +2840,6 @@
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
-      <c r="P74" s="4"/>
-      <c r="Q74" s="4"/>
-      <c r="R74" s="4"/>
-      <c r="S74" s="4"/>
     </row>
     <row r="75">
       <c r="A75" s="3"/>
@@ -3413,7 +2849,7 @@
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
+      <c r="H75" s="4"/>
       <c r="I75" s="4"/>
       <c r="J75" s="4"/>
       <c r="K75" s="4"/>
@@ -3421,10 +2857,6 @@
       <c r="M75" s="4"/>
       <c r="N75" s="4"/>
       <c r="O75" s="4"/>
-      <c r="P75" s="4"/>
-      <c r="Q75" s="4"/>
-      <c r="R75" s="4"/>
-      <c r="S75" s="4"/>
     </row>
     <row r="76">
       <c r="A76" s="3"/>
@@ -3434,7 +2866,7 @@
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
+      <c r="H76" s="4"/>
       <c r="I76" s="4"/>
       <c r="J76" s="4"/>
       <c r="K76" s="4"/>
@@ -3442,10 +2874,6 @@
       <c r="M76" s="4"/>
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
-      <c r="P76" s="4"/>
-      <c r="Q76" s="4"/>
-      <c r="R76" s="4"/>
-      <c r="S76" s="4"/>
     </row>
     <row r="77">
       <c r="A77" s="3"/>
@@ -3455,7 +2883,7 @@
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
+      <c r="H77" s="4"/>
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
       <c r="K77" s="4"/>
@@ -3463,10 +2891,6 @@
       <c r="M77" s="4"/>
       <c r="N77" s="4"/>
       <c r="O77" s="4"/>
-      <c r="P77" s="4"/>
-      <c r="Q77" s="4"/>
-      <c r="R77" s="4"/>
-      <c r="S77" s="4"/>
     </row>
     <row r="78">
       <c r="A78" s="3"/>
@@ -3476,7 +2900,7 @@
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
+      <c r="H78" s="4"/>
       <c r="I78" s="4"/>
       <c r="J78" s="4"/>
       <c r="K78" s="4"/>
@@ -3484,10 +2908,6 @@
       <c r="M78" s="4"/>
       <c r="N78" s="4"/>
       <c r="O78" s="4"/>
-      <c r="P78" s="4"/>
-      <c r="Q78" s="4"/>
-      <c r="R78" s="4"/>
-      <c r="S78" s="4"/>
     </row>
     <row r="79">
       <c r="A79" s="3"/>
@@ -3497,7 +2917,7 @@
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
+      <c r="H79" s="4"/>
       <c r="I79" s="4"/>
       <c r="J79" s="4"/>
       <c r="K79" s="4"/>
@@ -3505,10 +2925,6 @@
       <c r="M79" s="4"/>
       <c r="N79" s="4"/>
       <c r="O79" s="4"/>
-      <c r="P79" s="4"/>
-      <c r="Q79" s="4"/>
-      <c r="R79" s="4"/>
-      <c r="S79" s="4"/>
     </row>
     <row r="80">
       <c r="A80" s="3"/>
@@ -3518,7 +2934,7 @@
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
-      <c r="H80" s="3"/>
+      <c r="H80" s="4"/>
       <c r="I80" s="4"/>
       <c r="J80" s="4"/>
       <c r="K80" s="4"/>
@@ -3526,10 +2942,6 @@
       <c r="M80" s="4"/>
       <c r="N80" s="4"/>
       <c r="O80" s="4"/>
-      <c r="P80" s="4"/>
-      <c r="Q80" s="4"/>
-      <c r="R80" s="4"/>
-      <c r="S80" s="4"/>
     </row>
     <row r="81">
       <c r="A81" s="3"/>
@@ -3539,7 +2951,7 @@
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
-      <c r="H81" s="3"/>
+      <c r="H81" s="4"/>
       <c r="I81" s="4"/>
       <c r="J81" s="4"/>
       <c r="K81" s="4"/>
@@ -3547,10 +2959,6 @@
       <c r="M81" s="4"/>
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
-      <c r="P81" s="4"/>
-      <c r="Q81" s="4"/>
-      <c r="R81" s="4"/>
-      <c r="S81" s="4"/>
     </row>
     <row r="82">
       <c r="A82" s="3"/>
@@ -3560,7 +2968,7 @@
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
+      <c r="H82" s="4"/>
       <c r="I82" s="4"/>
       <c r="J82" s="4"/>
       <c r="K82" s="4"/>
@@ -3568,10 +2976,6 @@
       <c r="M82" s="4"/>
       <c r="N82" s="4"/>
       <c r="O82" s="4"/>
-      <c r="P82" s="4"/>
-      <c r="Q82" s="4"/>
-      <c r="R82" s="4"/>
-      <c r="S82" s="4"/>
     </row>
     <row r="83">
       <c r="A83" s="3"/>
@@ -3581,7 +2985,7 @@
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
-      <c r="H83" s="3"/>
+      <c r="H83" s="4"/>
       <c r="I83" s="4"/>
       <c r="J83" s="4"/>
       <c r="K83" s="4"/>
@@ -3589,10 +2993,6 @@
       <c r="M83" s="4"/>
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
-      <c r="P83" s="4"/>
-      <c r="Q83" s="4"/>
-      <c r="R83" s="4"/>
-      <c r="S83" s="4"/>
     </row>
     <row r="84">
       <c r="A84" s="3"/>
@@ -3602,7 +3002,7 @@
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
+      <c r="H84" s="4"/>
       <c r="I84" s="4"/>
       <c r="J84" s="4"/>
       <c r="K84" s="4"/>
@@ -3610,10 +3010,6 @@
       <c r="M84" s="4"/>
       <c r="N84" s="4"/>
       <c r="O84" s="4"/>
-      <c r="P84" s="4"/>
-      <c r="Q84" s="4"/>
-      <c r="R84" s="4"/>
-      <c r="S84" s="4"/>
     </row>
     <row r="85">
       <c r="A85" s="3"/>
@@ -3623,7 +3019,7 @@
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="3"/>
-      <c r="H85" s="3"/>
+      <c r="H85" s="4"/>
       <c r="I85" s="4"/>
       <c r="J85" s="4"/>
       <c r="K85" s="4"/>
@@ -3631,10 +3027,6 @@
       <c r="M85" s="4"/>
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
-      <c r="P85" s="4"/>
-      <c r="Q85" s="4"/>
-      <c r="R85" s="4"/>
-      <c r="S85" s="4"/>
     </row>
     <row r="86">
       <c r="A86" s="3"/>
@@ -3644,7 +3036,7 @@
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
+      <c r="H86" s="4"/>
       <c r="I86" s="4"/>
       <c r="J86" s="4"/>
       <c r="K86" s="4"/>
@@ -3652,10 +3044,6 @@
       <c r="M86" s="4"/>
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
-      <c r="P86" s="4"/>
-      <c r="Q86" s="4"/>
-      <c r="R86" s="4"/>
-      <c r="S86" s="4"/>
     </row>
     <row r="87">
       <c r="A87" s="3"/>
@@ -3665,7 +3053,7 @@
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
+      <c r="H87" s="4"/>
       <c r="I87" s="4"/>
       <c r="J87" s="4"/>
       <c r="K87" s="4"/>
@@ -3673,10 +3061,6 @@
       <c r="M87" s="4"/>
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
-      <c r="P87" s="4"/>
-      <c r="Q87" s="4"/>
-      <c r="R87" s="4"/>
-      <c r="S87" s="4"/>
     </row>
     <row r="88">
       <c r="A88" s="3"/>
@@ -3686,7 +3070,7 @@
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
-      <c r="H88" s="3"/>
+      <c r="H88" s="4"/>
       <c r="I88" s="4"/>
       <c r="J88" s="4"/>
       <c r="K88" s="4"/>
@@ -3694,10 +3078,6 @@
       <c r="M88" s="4"/>
       <c r="N88" s="4"/>
       <c r="O88" s="4"/>
-      <c r="P88" s="4"/>
-      <c r="Q88" s="4"/>
-      <c r="R88" s="4"/>
-      <c r="S88" s="4"/>
     </row>
     <row r="89">
       <c r="A89" s="3"/>
@@ -3707,7 +3087,7 @@
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
-      <c r="H89" s="3"/>
+      <c r="H89" s="4"/>
       <c r="I89" s="4"/>
       <c r="J89" s="4"/>
       <c r="K89" s="4"/>
@@ -3715,10 +3095,6 @@
       <c r="M89" s="4"/>
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
-      <c r="P89" s="4"/>
-      <c r="Q89" s="4"/>
-      <c r="R89" s="4"/>
-      <c r="S89" s="4"/>
     </row>
     <row r="90">
       <c r="A90" s="3"/>
@@ -3728,7 +3104,7 @@
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3"/>
-      <c r="H90" s="3"/>
+      <c r="H90" s="4"/>
       <c r="I90" s="4"/>
       <c r="J90" s="4"/>
       <c r="K90" s="4"/>
@@ -3736,10 +3112,6 @@
       <c r="M90" s="4"/>
       <c r="N90" s="4"/>
       <c r="O90" s="4"/>
-      <c r="P90" s="4"/>
-      <c r="Q90" s="4"/>
-      <c r="R90" s="4"/>
-      <c r="S90" s="4"/>
     </row>
     <row r="91">
       <c r="A91" s="3"/>
@@ -3749,7 +3121,7 @@
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
+      <c r="H91" s="4"/>
       <c r="I91" s="4"/>
       <c r="J91" s="4"/>
       <c r="K91" s="4"/>
@@ -3757,10 +3129,6 @@
       <c r="M91" s="4"/>
       <c r="N91" s="4"/>
       <c r="O91" s="4"/>
-      <c r="P91" s="4"/>
-      <c r="Q91" s="4"/>
-      <c r="R91" s="4"/>
-      <c r="S91" s="4"/>
     </row>
     <row r="92">
       <c r="A92" s="3"/>
@@ -3770,7 +3138,7 @@
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
+      <c r="H92" s="4"/>
       <c r="I92" s="4"/>
       <c r="J92" s="4"/>
       <c r="K92" s="4"/>
@@ -3778,10 +3146,6 @@
       <c r="M92" s="4"/>
       <c r="N92" s="4"/>
       <c r="O92" s="4"/>
-      <c r="P92" s="4"/>
-      <c r="Q92" s="4"/>
-      <c r="R92" s="4"/>
-      <c r="S92" s="4"/>
     </row>
     <row r="93">
       <c r="A93" s="3"/>
@@ -3791,7 +3155,7 @@
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3"/>
-      <c r="H93" s="3"/>
+      <c r="H93" s="4"/>
       <c r="I93" s="4"/>
       <c r="J93" s="4"/>
       <c r="K93" s="4"/>
@@ -3799,10 +3163,6 @@
       <c r="M93" s="4"/>
       <c r="N93" s="4"/>
       <c r="O93" s="4"/>
-      <c r="P93" s="4"/>
-      <c r="Q93" s="4"/>
-      <c r="R93" s="4"/>
-      <c r="S93" s="4"/>
     </row>
     <row r="94">
       <c r="A94" s="3"/>
@@ -3812,7 +3172,7 @@
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3"/>
-      <c r="H94" s="3"/>
+      <c r="H94" s="4"/>
       <c r="I94" s="4"/>
       <c r="J94" s="4"/>
       <c r="K94" s="4"/>
@@ -3820,10 +3180,6 @@
       <c r="M94" s="4"/>
       <c r="N94" s="4"/>
       <c r="O94" s="4"/>
-      <c r="P94" s="4"/>
-      <c r="Q94" s="4"/>
-      <c r="R94" s="4"/>
-      <c r="S94" s="4"/>
     </row>
     <row r="95">
       <c r="A95" s="3"/>
@@ -3833,7 +3189,7 @@
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
+      <c r="H95" s="4"/>
       <c r="I95" s="4"/>
       <c r="J95" s="4"/>
       <c r="K95" s="4"/>
@@ -3841,10 +3197,6 @@
       <c r="M95" s="4"/>
       <c r="N95" s="4"/>
       <c r="O95" s="4"/>
-      <c r="P95" s="4"/>
-      <c r="Q95" s="4"/>
-      <c r="R95" s="4"/>
-      <c r="S95" s="4"/>
     </row>
     <row r="96">
       <c r="A96" s="3"/>
@@ -3854,7 +3206,7 @@
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
-      <c r="H96" s="3"/>
+      <c r="H96" s="4"/>
       <c r="I96" s="4"/>
       <c r="J96" s="4"/>
       <c r="K96" s="4"/>
@@ -3862,10 +3214,6 @@
       <c r="M96" s="4"/>
       <c r="N96" s="4"/>
       <c r="O96" s="4"/>
-      <c r="P96" s="4"/>
-      <c r="Q96" s="4"/>
-      <c r="R96" s="4"/>
-      <c r="S96" s="4"/>
     </row>
     <row r="97">
       <c r="A97" s="3"/>
@@ -3875,7 +3223,7 @@
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
       <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
+      <c r="H97" s="4"/>
       <c r="I97" s="4"/>
       <c r="J97" s="4"/>
       <c r="K97" s="4"/>
@@ -3883,10 +3231,6 @@
       <c r="M97" s="4"/>
       <c r="N97" s="4"/>
       <c r="O97" s="4"/>
-      <c r="P97" s="4"/>
-      <c r="Q97" s="4"/>
-      <c r="R97" s="4"/>
-      <c r="S97" s="4"/>
     </row>
     <row r="98">
       <c r="A98" s="3"/>
@@ -3896,7 +3240,7 @@
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
       <c r="G98" s="3"/>
-      <c r="H98" s="3"/>
+      <c r="H98" s="4"/>
       <c r="I98" s="4"/>
       <c r="J98" s="4"/>
       <c r="K98" s="4"/>
@@ -3904,10 +3248,6 @@
       <c r="M98" s="4"/>
       <c r="N98" s="4"/>
       <c r="O98" s="4"/>
-      <c r="P98" s="4"/>
-      <c r="Q98" s="4"/>
-      <c r="R98" s="4"/>
-      <c r="S98" s="4"/>
     </row>
     <row r="99">
       <c r="A99" s="3"/>
@@ -3917,7 +3257,7 @@
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
-      <c r="H99" s="3"/>
+      <c r="H99" s="4"/>
       <c r="I99" s="4"/>
       <c r="J99" s="4"/>
       <c r="K99" s="4"/>
@@ -3925,10 +3265,6 @@
       <c r="M99" s="4"/>
       <c r="N99" s="4"/>
       <c r="O99" s="4"/>
-      <c r="P99" s="4"/>
-      <c r="Q99" s="4"/>
-      <c r="R99" s="4"/>
-      <c r="S99" s="4"/>
     </row>
     <row r="100">
       <c r="A100" s="3"/>
@@ -3938,7 +3274,7 @@
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
-      <c r="H100" s="3"/>
+      <c r="H100" s="4"/>
       <c r="I100" s="4"/>
       <c r="J100" s="4"/>
       <c r="K100" s="4"/>
@@ -3946,10 +3282,6 @@
       <c r="M100" s="4"/>
       <c r="N100" s="4"/>
       <c r="O100" s="4"/>
-      <c r="P100" s="4"/>
-      <c r="Q100" s="4"/>
-      <c r="R100" s="4"/>
-      <c r="S100" s="4"/>
     </row>
     <row r="101">
       <c r="A101" s="3"/>
@@ -3959,7 +3291,7 @@
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
-      <c r="H101" s="3"/>
+      <c r="H101" s="4"/>
       <c r="I101" s="4"/>
       <c r="J101" s="4"/>
       <c r="K101" s="4"/>
@@ -3967,10 +3299,6 @@
       <c r="M101" s="4"/>
       <c r="N101" s="4"/>
       <c r="O101" s="4"/>
-      <c r="P101" s="4"/>
-      <c r="Q101" s="4"/>
-      <c r="R101" s="4"/>
-      <c r="S101" s="4"/>
     </row>
     <row r="102">
       <c r="A102" s="3"/>
@@ -3980,7 +3308,7 @@
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
       <c r="G102" s="3"/>
-      <c r="H102" s="3"/>
+      <c r="H102" s="4"/>
       <c r="I102" s="4"/>
       <c r="J102" s="4"/>
       <c r="K102" s="4"/>
@@ -3988,10 +3316,6 @@
       <c r="M102" s="4"/>
       <c r="N102" s="4"/>
       <c r="O102" s="4"/>
-      <c r="P102" s="4"/>
-      <c r="Q102" s="4"/>
-      <c r="R102" s="4"/>
-      <c r="S102" s="4"/>
     </row>
     <row r="103">
       <c r="A103" s="3"/>
@@ -4001,7 +3325,7 @@
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
-      <c r="H103" s="3"/>
+      <c r="H103" s="4"/>
       <c r="I103" s="4"/>
       <c r="J103" s="4"/>
       <c r="K103" s="4"/>
@@ -4009,10 +3333,6 @@
       <c r="M103" s="4"/>
       <c r="N103" s="4"/>
       <c r="O103" s="4"/>
-      <c r="P103" s="4"/>
-      <c r="Q103" s="4"/>
-      <c r="R103" s="4"/>
-      <c r="S103" s="4"/>
     </row>
     <row r="104">
       <c r="A104" s="3"/>
@@ -4022,7 +3342,7 @@
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
-      <c r="H104" s="3"/>
+      <c r="H104" s="4"/>
       <c r="I104" s="4"/>
       <c r="J104" s="4"/>
       <c r="K104" s="4"/>
@@ -4030,10 +3350,6 @@
       <c r="M104" s="4"/>
       <c r="N104" s="4"/>
       <c r="O104" s="4"/>
-      <c r="P104" s="4"/>
-      <c r="Q104" s="4"/>
-      <c r="R104" s="4"/>
-      <c r="S104" s="4"/>
     </row>
     <row r="105">
       <c r="A105" s="3"/>
@@ -4043,7 +3359,7 @@
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
-      <c r="H105" s="3"/>
+      <c r="H105" s="4"/>
       <c r="I105" s="4"/>
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
@@ -4051,10 +3367,6 @@
       <c r="M105" s="4"/>
       <c r="N105" s="4"/>
       <c r="O105" s="4"/>
-      <c r="P105" s="4"/>
-      <c r="Q105" s="4"/>
-      <c r="R105" s="4"/>
-      <c r="S105" s="4"/>
     </row>
     <row r="106">
       <c r="A106" s="3"/>
@@ -4064,7 +3376,7 @@
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
-      <c r="H106" s="3"/>
+      <c r="H106" s="4"/>
       <c r="I106" s="4"/>
       <c r="J106" s="4"/>
       <c r="K106" s="4"/>
@@ -4072,10 +3384,6 @@
       <c r="M106" s="4"/>
       <c r="N106" s="4"/>
       <c r="O106" s="4"/>
-      <c r="P106" s="4"/>
-      <c r="Q106" s="4"/>
-      <c r="R106" s="4"/>
-      <c r="S106" s="4"/>
     </row>
     <row r="107">
       <c r="A107" s="3"/>
@@ -4085,7 +3393,7 @@
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
-      <c r="H107" s="3"/>
+      <c r="H107" s="4"/>
       <c r="I107" s="4"/>
       <c r="J107" s="4"/>
       <c r="K107" s="4"/>
@@ -4093,10 +3401,6 @@
       <c r="M107" s="4"/>
       <c r="N107" s="4"/>
       <c r="O107" s="4"/>
-      <c r="P107" s="4"/>
-      <c r="Q107" s="4"/>
-      <c r="R107" s="4"/>
-      <c r="S107" s="4"/>
     </row>
     <row r="108">
       <c r="A108" s="3"/>
@@ -4106,7 +3410,7 @@
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
-      <c r="H108" s="3"/>
+      <c r="H108" s="4"/>
       <c r="I108" s="4"/>
       <c r="J108" s="4"/>
       <c r="K108" s="4"/>
@@ -4114,10 +3418,6 @@
       <c r="M108" s="4"/>
       <c r="N108" s="4"/>
       <c r="O108" s="4"/>
-      <c r="P108" s="4"/>
-      <c r="Q108" s="4"/>
-      <c r="R108" s="4"/>
-      <c r="S108" s="4"/>
     </row>
     <row r="109">
       <c r="A109" s="3"/>
@@ -4127,7 +3427,7 @@
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
       <c r="G109" s="3"/>
-      <c r="H109" s="3"/>
+      <c r="H109" s="4"/>
       <c r="I109" s="4"/>
       <c r="J109" s="4"/>
       <c r="K109" s="4"/>
@@ -4135,10 +3435,6 @@
       <c r="M109" s="4"/>
       <c r="N109" s="4"/>
       <c r="O109" s="4"/>
-      <c r="P109" s="4"/>
-      <c r="Q109" s="4"/>
-      <c r="R109" s="4"/>
-      <c r="S109" s="4"/>
     </row>
     <row r="110">
       <c r="A110" s="3"/>
@@ -4148,7 +3444,7 @@
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
       <c r="G110" s="3"/>
-      <c r="H110" s="3"/>
+      <c r="H110" s="4"/>
       <c r="I110" s="4"/>
       <c r="J110" s="4"/>
       <c r="K110" s="4"/>
@@ -4156,10 +3452,6 @@
       <c r="M110" s="4"/>
       <c r="N110" s="4"/>
       <c r="O110" s="4"/>
-      <c r="P110" s="4"/>
-      <c r="Q110" s="4"/>
-      <c r="R110" s="4"/>
-      <c r="S110" s="4"/>
     </row>
     <row r="111">
       <c r="A111" s="3"/>
@@ -4169,7 +3461,7 @@
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
       <c r="G111" s="3"/>
-      <c r="H111" s="3"/>
+      <c r="H111" s="4"/>
       <c r="I111" s="4"/>
       <c r="J111" s="4"/>
       <c r="K111" s="4"/>
@@ -4177,10 +3469,6 @@
       <c r="M111" s="4"/>
       <c r="N111" s="4"/>
       <c r="O111" s="4"/>
-      <c r="P111" s="4"/>
-      <c r="Q111" s="4"/>
-      <c r="R111" s="4"/>
-      <c r="S111" s="4"/>
     </row>
     <row r="112">
       <c r="A112" s="3"/>
@@ -4190,7 +3478,7 @@
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
       <c r="G112" s="3"/>
-      <c r="H112" s="3"/>
+      <c r="H112" s="4"/>
       <c r="I112" s="4"/>
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
@@ -4198,10 +3486,6 @@
       <c r="M112" s="4"/>
       <c r="N112" s="4"/>
       <c r="O112" s="4"/>
-      <c r="P112" s="4"/>
-      <c r="Q112" s="4"/>
-      <c r="R112" s="4"/>
-      <c r="S112" s="4"/>
     </row>
     <row r="113">
       <c r="A113" s="3"/>
@@ -4211,7 +3495,7 @@
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
       <c r="G113" s="3"/>
-      <c r="H113" s="3"/>
+      <c r="H113" s="4"/>
       <c r="I113" s="4"/>
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
@@ -4219,10 +3503,6 @@
       <c r="M113" s="4"/>
       <c r="N113" s="4"/>
       <c r="O113" s="4"/>
-      <c r="P113" s="4"/>
-      <c r="Q113" s="4"/>
-      <c r="R113" s="4"/>
-      <c r="S113" s="4"/>
     </row>
     <row r="114">
       <c r="A114" s="3"/>
@@ -4232,7 +3512,7 @@
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
       <c r="G114" s="3"/>
-      <c r="H114" s="3"/>
+      <c r="H114" s="4"/>
       <c r="I114" s="4"/>
       <c r="J114" s="4"/>
       <c r="K114" s="4"/>
@@ -4240,10 +3520,6 @@
       <c r="M114" s="4"/>
       <c r="N114" s="4"/>
       <c r="O114" s="4"/>
-      <c r="P114" s="4"/>
-      <c r="Q114" s="4"/>
-      <c r="R114" s="4"/>
-      <c r="S114" s="4"/>
     </row>
     <row r="115">
       <c r="A115" s="3"/>
@@ -4253,7 +3529,7 @@
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
       <c r="G115" s="3"/>
-      <c r="H115" s="3"/>
+      <c r="H115" s="4"/>
       <c r="I115" s="4"/>
       <c r="J115" s="4"/>
       <c r="K115" s="4"/>
@@ -4261,10 +3537,6 @@
       <c r="M115" s="4"/>
       <c r="N115" s="4"/>
       <c r="O115" s="4"/>
-      <c r="P115" s="4"/>
-      <c r="Q115" s="4"/>
-      <c r="R115" s="4"/>
-      <c r="S115" s="4"/>
     </row>
     <row r="116">
       <c r="A116" s="3"/>
@@ -4274,7 +3546,7 @@
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
       <c r="G116" s="3"/>
-      <c r="H116" s="3"/>
+      <c r="H116" s="4"/>
       <c r="I116" s="4"/>
       <c r="J116" s="4"/>
       <c r="K116" s="4"/>
@@ -4282,10 +3554,6 @@
       <c r="M116" s="4"/>
       <c r="N116" s="4"/>
       <c r="O116" s="4"/>
-      <c r="P116" s="4"/>
-      <c r="Q116" s="4"/>
-      <c r="R116" s="4"/>
-      <c r="S116" s="4"/>
     </row>
     <row r="117">
       <c r="A117" s="3"/>
@@ -4295,7 +3563,7 @@
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
       <c r="G117" s="3"/>
-      <c r="H117" s="3"/>
+      <c r="H117" s="4"/>
       <c r="I117" s="4"/>
       <c r="J117" s="4"/>
       <c r="K117" s="4"/>
@@ -4303,10 +3571,6 @@
       <c r="M117" s="4"/>
       <c r="N117" s="4"/>
       <c r="O117" s="4"/>
-      <c r="P117" s="4"/>
-      <c r="Q117" s="4"/>
-      <c r="R117" s="4"/>
-      <c r="S117" s="4"/>
     </row>
     <row r="118">
       <c r="A118" s="3"/>
@@ -4316,7 +3580,7 @@
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
       <c r="G118" s="3"/>
-      <c r="H118" s="3"/>
+      <c r="H118" s="4"/>
       <c r="I118" s="4"/>
       <c r="J118" s="4"/>
       <c r="K118" s="4"/>
@@ -4324,10 +3588,6 @@
       <c r="M118" s="4"/>
       <c r="N118" s="4"/>
       <c r="O118" s="4"/>
-      <c r="P118" s="4"/>
-      <c r="Q118" s="4"/>
-      <c r="R118" s="4"/>
-      <c r="S118" s="4"/>
     </row>
     <row r="119">
       <c r="A119" s="3"/>
@@ -4337,7 +3597,7 @@
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
       <c r="G119" s="3"/>
-      <c r="H119" s="3"/>
+      <c r="H119" s="4"/>
       <c r="I119" s="4"/>
       <c r="J119" s="4"/>
       <c r="K119" s="4"/>
@@ -4345,10 +3605,6 @@
       <c r="M119" s="4"/>
       <c r="N119" s="4"/>
       <c r="O119" s="4"/>
-      <c r="P119" s="4"/>
-      <c r="Q119" s="4"/>
-      <c r="R119" s="4"/>
-      <c r="S119" s="4"/>
     </row>
     <row r="120">
       <c r="A120" s="3"/>
@@ -4358,7 +3614,7 @@
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
       <c r="G120" s="3"/>
-      <c r="H120" s="3"/>
+      <c r="H120" s="4"/>
       <c r="I120" s="4"/>
       <c r="J120" s="4"/>
       <c r="K120" s="4"/>
@@ -4366,10 +3622,6 @@
       <c r="M120" s="4"/>
       <c r="N120" s="4"/>
       <c r="O120" s="4"/>
-      <c r="P120" s="4"/>
-      <c r="Q120" s="4"/>
-      <c r="R120" s="4"/>
-      <c r="S120" s="4"/>
     </row>
     <row r="121">
       <c r="A121" s="3"/>
@@ -4379,7 +3631,7 @@
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
       <c r="G121" s="3"/>
-      <c r="H121" s="3"/>
+      <c r="H121" s="4"/>
       <c r="I121" s="4"/>
       <c r="J121" s="4"/>
       <c r="K121" s="4"/>
@@ -4387,10 +3639,6 @@
       <c r="M121" s="4"/>
       <c r="N121" s="4"/>
       <c r="O121" s="4"/>
-      <c r="P121" s="4"/>
-      <c r="Q121" s="4"/>
-      <c r="R121" s="4"/>
-      <c r="S121" s="4"/>
     </row>
     <row r="122">
       <c r="A122" s="3"/>
@@ -4400,7 +3648,7 @@
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
       <c r="G122" s="3"/>
-      <c r="H122" s="3"/>
+      <c r="H122" s="4"/>
       <c r="I122" s="4"/>
       <c r="J122" s="4"/>
       <c r="K122" s="4"/>
@@ -4408,10 +3656,6 @@
       <c r="M122" s="4"/>
       <c r="N122" s="4"/>
       <c r="O122" s="4"/>
-      <c r="P122" s="4"/>
-      <c r="Q122" s="4"/>
-      <c r="R122" s="4"/>
-      <c r="S122" s="4"/>
     </row>
     <row r="123">
       <c r="A123" s="3"/>
@@ -4421,7 +3665,7 @@
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
       <c r="G123" s="3"/>
-      <c r="H123" s="3"/>
+      <c r="H123" s="4"/>
       <c r="I123" s="4"/>
       <c r="J123" s="4"/>
       <c r="K123" s="4"/>
@@ -4429,10 +3673,6 @@
       <c r="M123" s="4"/>
       <c r="N123" s="4"/>
       <c r="O123" s="4"/>
-      <c r="P123" s="4"/>
-      <c r="Q123" s="4"/>
-      <c r="R123" s="4"/>
-      <c r="S123" s="4"/>
     </row>
     <row r="124">
       <c r="A124" s="3"/>
@@ -4442,7 +3682,7 @@
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
       <c r="G124" s="3"/>
-      <c r="H124" s="3"/>
+      <c r="H124" s="4"/>
       <c r="I124" s="4"/>
       <c r="J124" s="4"/>
       <c r="K124" s="4"/>
@@ -4450,10 +3690,6 @@
       <c r="M124" s="4"/>
       <c r="N124" s="4"/>
       <c r="O124" s="4"/>
-      <c r="P124" s="4"/>
-      <c r="Q124" s="4"/>
-      <c r="R124" s="4"/>
-      <c r="S124" s="4"/>
     </row>
     <row r="125">
       <c r="A125" s="3"/>
@@ -4463,7 +3699,7 @@
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
       <c r="G125" s="3"/>
-      <c r="H125" s="3"/>
+      <c r="H125" s="4"/>
       <c r="I125" s="4"/>
       <c r="J125" s="4"/>
       <c r="K125" s="4"/>
@@ -4471,10 +3707,6 @@
       <c r="M125" s="4"/>
       <c r="N125" s="4"/>
       <c r="O125" s="4"/>
-      <c r="P125" s="4"/>
-      <c r="Q125" s="4"/>
-      <c r="R125" s="4"/>
-      <c r="S125" s="4"/>
     </row>
     <row r="126">
       <c r="A126" s="3"/>
@@ -4484,7 +3716,7 @@
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
       <c r="G126" s="3"/>
-      <c r="H126" s="3"/>
+      <c r="H126" s="4"/>
       <c r="I126" s="4"/>
       <c r="J126" s="4"/>
       <c r="K126" s="4"/>
@@ -4492,10 +3724,6 @@
       <c r="M126" s="4"/>
       <c r="N126" s="4"/>
       <c r="O126" s="4"/>
-      <c r="P126" s="4"/>
-      <c r="Q126" s="4"/>
-      <c r="R126" s="4"/>
-      <c r="S126" s="4"/>
     </row>
     <row r="127">
       <c r="A127" s="3"/>
@@ -4505,7 +3733,7 @@
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
       <c r="G127" s="3"/>
-      <c r="H127" s="3"/>
+      <c r="H127" s="4"/>
       <c r="I127" s="4"/>
       <c r="J127" s="4"/>
       <c r="K127" s="4"/>
@@ -4513,10 +3741,6 @@
       <c r="M127" s="4"/>
       <c r="N127" s="4"/>
       <c r="O127" s="4"/>
-      <c r="P127" s="4"/>
-      <c r="Q127" s="4"/>
-      <c r="R127" s="4"/>
-      <c r="S127" s="4"/>
     </row>
     <row r="128">
       <c r="A128" s="3"/>
@@ -4526,7 +3750,7 @@
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
       <c r="G128" s="3"/>
-      <c r="H128" s="3"/>
+      <c r="H128" s="4"/>
       <c r="I128" s="4"/>
       <c r="J128" s="4"/>
       <c r="K128" s="4"/>
@@ -4534,10 +3758,6 @@
       <c r="M128" s="4"/>
       <c r="N128" s="4"/>
       <c r="O128" s="4"/>
-      <c r="P128" s="4"/>
-      <c r="Q128" s="4"/>
-      <c r="R128" s="4"/>
-      <c r="S128" s="4"/>
     </row>
     <row r="129">
       <c r="A129" s="3"/>
@@ -4547,7 +3767,7 @@
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
       <c r="G129" s="3"/>
-      <c r="H129" s="3"/>
+      <c r="H129" s="4"/>
       <c r="I129" s="4"/>
       <c r="J129" s="4"/>
       <c r="K129" s="4"/>
@@ -4555,10 +3775,6 @@
       <c r="M129" s="4"/>
       <c r="N129" s="4"/>
       <c r="O129" s="4"/>
-      <c r="P129" s="4"/>
-      <c r="Q129" s="4"/>
-      <c r="R129" s="4"/>
-      <c r="S129" s="4"/>
     </row>
     <row r="130">
       <c r="A130" s="3"/>
@@ -4568,7 +3784,7 @@
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
       <c r="G130" s="3"/>
-      <c r="H130" s="3"/>
+      <c r="H130" s="4"/>
       <c r="I130" s="4"/>
       <c r="J130" s="4"/>
       <c r="K130" s="4"/>
@@ -4576,10 +3792,6 @@
       <c r="M130" s="4"/>
       <c r="N130" s="4"/>
       <c r="O130" s="4"/>
-      <c r="P130" s="4"/>
-      <c r="Q130" s="4"/>
-      <c r="R130" s="4"/>
-      <c r="S130" s="4"/>
     </row>
     <row r="131">
       <c r="A131" s="3"/>
@@ -4589,7 +3801,7 @@
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
       <c r="G131" s="3"/>
-      <c r="H131" s="3"/>
+      <c r="H131" s="4"/>
       <c r="I131" s="4"/>
       <c r="J131" s="4"/>
       <c r="K131" s="4"/>
@@ -4597,10 +3809,6 @@
       <c r="M131" s="4"/>
       <c r="N131" s="4"/>
       <c r="O131" s="4"/>
-      <c r="P131" s="4"/>
-      <c r="Q131" s="4"/>
-      <c r="R131" s="4"/>
-      <c r="S131" s="4"/>
     </row>
     <row r="132">
       <c r="A132" s="3"/>
@@ -4610,7 +3818,7 @@
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
       <c r="G132" s="3"/>
-      <c r="H132" s="3"/>
+      <c r="H132" s="4"/>
       <c r="I132" s="4"/>
       <c r="J132" s="4"/>
       <c r="K132" s="4"/>
@@ -4618,10 +3826,6 @@
       <c r="M132" s="4"/>
       <c r="N132" s="4"/>
       <c r="O132" s="4"/>
-      <c r="P132" s="4"/>
-      <c r="Q132" s="4"/>
-      <c r="R132" s="4"/>
-      <c r="S132" s="4"/>
     </row>
     <row r="133">
       <c r="A133" s="3"/>
@@ -4631,7 +3835,7 @@
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
       <c r="G133" s="3"/>
-      <c r="H133" s="3"/>
+      <c r="H133" s="4"/>
       <c r="I133" s="4"/>
       <c r="J133" s="4"/>
       <c r="K133" s="4"/>
@@ -4639,10 +3843,6 @@
       <c r="M133" s="4"/>
       <c r="N133" s="4"/>
       <c r="O133" s="4"/>
-      <c r="P133" s="4"/>
-      <c r="Q133" s="4"/>
-      <c r="R133" s="4"/>
-      <c r="S133" s="4"/>
     </row>
     <row r="134">
       <c r="A134" s="3"/>
@@ -4652,7 +3852,7 @@
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
       <c r="G134" s="3"/>
-      <c r="H134" s="3"/>
+      <c r="H134" s="4"/>
       <c r="I134" s="4"/>
       <c r="J134" s="4"/>
       <c r="K134" s="4"/>
@@ -4660,10 +3860,6 @@
       <c r="M134" s="4"/>
       <c r="N134" s="4"/>
       <c r="O134" s="4"/>
-      <c r="P134" s="4"/>
-      <c r="Q134" s="4"/>
-      <c r="R134" s="4"/>
-      <c r="S134" s="4"/>
     </row>
     <row r="135">
       <c r="A135" s="3"/>
@@ -4673,7 +3869,7 @@
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
       <c r="G135" s="3"/>
-      <c r="H135" s="3"/>
+      <c r="H135" s="4"/>
       <c r="I135" s="4"/>
       <c r="J135" s="4"/>
       <c r="K135" s="4"/>
@@ -4681,10 +3877,6 @@
       <c r="M135" s="4"/>
       <c r="N135" s="4"/>
       <c r="O135" s="4"/>
-      <c r="P135" s="4"/>
-      <c r="Q135" s="4"/>
-      <c r="R135" s="4"/>
-      <c r="S135" s="4"/>
     </row>
     <row r="136">
       <c r="A136" s="3"/>
@@ -4694,7 +3886,7 @@
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
       <c r="G136" s="3"/>
-      <c r="H136" s="3"/>
+      <c r="H136" s="4"/>
       <c r="I136" s="4"/>
       <c r="J136" s="4"/>
       <c r="K136" s="4"/>
@@ -4702,10 +3894,6 @@
       <c r="M136" s="4"/>
       <c r="N136" s="4"/>
       <c r="O136" s="4"/>
-      <c r="P136" s="4"/>
-      <c r="Q136" s="4"/>
-      <c r="R136" s="4"/>
-      <c r="S136" s="4"/>
     </row>
     <row r="137">
       <c r="A137" s="3"/>
@@ -4715,7 +3903,7 @@
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
       <c r="G137" s="3"/>
-      <c r="H137" s="3"/>
+      <c r="H137" s="4"/>
       <c r="I137" s="4"/>
       <c r="J137" s="4"/>
       <c r="K137" s="4"/>
@@ -4723,10 +3911,6 @@
       <c r="M137" s="4"/>
       <c r="N137" s="4"/>
       <c r="O137" s="4"/>
-      <c r="P137" s="4"/>
-      <c r="Q137" s="4"/>
-      <c r="R137" s="4"/>
-      <c r="S137" s="4"/>
     </row>
     <row r="138">
       <c r="A138" s="3"/>
@@ -4736,7 +3920,7 @@
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
       <c r="G138" s="3"/>
-      <c r="H138" s="3"/>
+      <c r="H138" s="4"/>
       <c r="I138" s="4"/>
       <c r="J138" s="4"/>
       <c r="K138" s="4"/>
@@ -4744,10 +3928,6 @@
       <c r="M138" s="4"/>
       <c r="N138" s="4"/>
       <c r="O138" s="4"/>
-      <c r="P138" s="4"/>
-      <c r="Q138" s="4"/>
-      <c r="R138" s="4"/>
-      <c r="S138" s="4"/>
     </row>
     <row r="139">
       <c r="A139" s="3"/>
@@ -4757,7 +3937,7 @@
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
       <c r="G139" s="3"/>
-      <c r="H139" s="3"/>
+      <c r="H139" s="4"/>
       <c r="I139" s="4"/>
       <c r="J139" s="4"/>
       <c r="K139" s="4"/>
@@ -4765,10 +3945,6 @@
       <c r="M139" s="4"/>
       <c r="N139" s="4"/>
       <c r="O139" s="4"/>
-      <c r="P139" s="4"/>
-      <c r="Q139" s="4"/>
-      <c r="R139" s="4"/>
-      <c r="S139" s="4"/>
     </row>
     <row r="140">
       <c r="A140" s="3"/>
@@ -4778,7 +3954,7 @@
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
       <c r="G140" s="3"/>
-      <c r="H140" s="3"/>
+      <c r="H140" s="4"/>
       <c r="I140" s="4"/>
       <c r="J140" s="4"/>
       <c r="K140" s="4"/>
@@ -4786,10 +3962,6 @@
       <c r="M140" s="4"/>
       <c r="N140" s="4"/>
       <c r="O140" s="4"/>
-      <c r="P140" s="4"/>
-      <c r="Q140" s="4"/>
-      <c r="R140" s="4"/>
-      <c r="S140" s="4"/>
     </row>
     <row r="141">
       <c r="A141" s="3"/>
@@ -4799,7 +3971,7 @@
       <c r="E141" s="3"/>
       <c r="F141" s="3"/>
       <c r="G141" s="3"/>
-      <c r="H141" s="3"/>
+      <c r="H141" s="4"/>
       <c r="I141" s="4"/>
       <c r="J141" s="4"/>
       <c r="K141" s="4"/>
@@ -4807,10 +3979,6 @@
       <c r="M141" s="4"/>
       <c r="N141" s="4"/>
       <c r="O141" s="4"/>
-      <c r="P141" s="4"/>
-      <c r="Q141" s="4"/>
-      <c r="R141" s="4"/>
-      <c r="S141" s="4"/>
     </row>
     <row r="142">
       <c r="A142" s="3"/>
@@ -4820,7 +3988,7 @@
       <c r="E142" s="3"/>
       <c r="F142" s="3"/>
       <c r="G142" s="3"/>
-      <c r="H142" s="3"/>
+      <c r="H142" s="4"/>
       <c r="I142" s="4"/>
       <c r="J142" s="4"/>
       <c r="K142" s="4"/>
@@ -4828,10 +3996,6 @@
       <c r="M142" s="4"/>
       <c r="N142" s="4"/>
       <c r="O142" s="4"/>
-      <c r="P142" s="4"/>
-      <c r="Q142" s="4"/>
-      <c r="R142" s="4"/>
-      <c r="S142" s="4"/>
     </row>
     <row r="143">
       <c r="A143" s="3"/>
@@ -4841,7 +4005,7 @@
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
       <c r="G143" s="3"/>
-      <c r="H143" s="3"/>
+      <c r="H143" s="4"/>
       <c r="I143" s="4"/>
       <c r="J143" s="4"/>
       <c r="K143" s="4"/>
@@ -4849,10 +4013,6 @@
       <c r="M143" s="4"/>
       <c r="N143" s="4"/>
       <c r="O143" s="4"/>
-      <c r="P143" s="4"/>
-      <c r="Q143" s="4"/>
-      <c r="R143" s="4"/>
-      <c r="S143" s="4"/>
     </row>
     <row r="144">
       <c r="A144" s="3"/>
@@ -4862,7 +4022,7 @@
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
       <c r="G144" s="3"/>
-      <c r="H144" s="3"/>
+      <c r="H144" s="4"/>
       <c r="I144" s="4"/>
       <c r="J144" s="4"/>
       <c r="K144" s="4"/>
@@ -4870,10 +4030,6 @@
       <c r="M144" s="4"/>
       <c r="N144" s="4"/>
       <c r="O144" s="4"/>
-      <c r="P144" s="4"/>
-      <c r="Q144" s="4"/>
-      <c r="R144" s="4"/>
-      <c r="S144" s="4"/>
     </row>
     <row r="145">
       <c r="A145" s="3"/>
@@ -4883,7 +4039,7 @@
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
       <c r="G145" s="3"/>
-      <c r="H145" s="3"/>
+      <c r="H145" s="4"/>
       <c r="I145" s="4"/>
       <c r="J145" s="4"/>
       <c r="K145" s="4"/>
@@ -4891,10 +4047,6 @@
       <c r="M145" s="4"/>
       <c r="N145" s="4"/>
       <c r="O145" s="4"/>
-      <c r="P145" s="4"/>
-      <c r="Q145" s="4"/>
-      <c r="R145" s="4"/>
-      <c r="S145" s="4"/>
     </row>
     <row r="146">
       <c r="A146" s="3"/>
@@ -4904,7 +4056,7 @@
       <c r="E146" s="3"/>
       <c r="F146" s="3"/>
       <c r="G146" s="3"/>
-      <c r="H146" s="3"/>
+      <c r="H146" s="4"/>
       <c r="I146" s="4"/>
       <c r="J146" s="4"/>
       <c r="K146" s="4"/>
@@ -4912,10 +4064,6 @@
       <c r="M146" s="4"/>
       <c r="N146" s="4"/>
       <c r="O146" s="4"/>
-      <c r="P146" s="4"/>
-      <c r="Q146" s="4"/>
-      <c r="R146" s="4"/>
-      <c r="S146" s="4"/>
     </row>
     <row r="147">
       <c r="A147" s="3"/>
@@ -4925,7 +4073,7 @@
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
       <c r="G147" s="3"/>
-      <c r="H147" s="3"/>
+      <c r="H147" s="4"/>
       <c r="I147" s="4"/>
       <c r="J147" s="4"/>
       <c r="K147" s="4"/>
@@ -4933,10 +4081,6 @@
       <c r="M147" s="4"/>
       <c r="N147" s="4"/>
       <c r="O147" s="4"/>
-      <c r="P147" s="4"/>
-      <c r="Q147" s="4"/>
-      <c r="R147" s="4"/>
-      <c r="S147" s="4"/>
     </row>
     <row r="148">
       <c r="A148" s="3"/>
@@ -4946,7 +4090,7 @@
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
       <c r="G148" s="3"/>
-      <c r="H148" s="3"/>
+      <c r="H148" s="4"/>
       <c r="I148" s="4"/>
       <c r="J148" s="4"/>
       <c r="K148" s="4"/>
@@ -4954,10 +4098,6 @@
       <c r="M148" s="4"/>
       <c r="N148" s="4"/>
       <c r="O148" s="4"/>
-      <c r="P148" s="4"/>
-      <c r="Q148" s="4"/>
-      <c r="R148" s="4"/>
-      <c r="S148" s="4"/>
     </row>
     <row r="149">
       <c r="A149" s="3"/>
@@ -4967,7 +4107,7 @@
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
       <c r="G149" s="3"/>
-      <c r="H149" s="3"/>
+      <c r="H149" s="4"/>
       <c r="I149" s="4"/>
       <c r="J149" s="4"/>
       <c r="K149" s="4"/>
@@ -4975,10 +4115,6 @@
       <c r="M149" s="4"/>
       <c r="N149" s="4"/>
       <c r="O149" s="4"/>
-      <c r="P149" s="4"/>
-      <c r="Q149" s="4"/>
-      <c r="R149" s="4"/>
-      <c r="S149" s="4"/>
     </row>
     <row r="150">
       <c r="A150" s="3"/>
@@ -4988,7 +4124,7 @@
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
       <c r="G150" s="3"/>
-      <c r="H150" s="3"/>
+      <c r="H150" s="4"/>
       <c r="I150" s="4"/>
       <c r="J150" s="4"/>
       <c r="K150" s="4"/>
@@ -4996,10 +4132,6 @@
       <c r="M150" s="4"/>
       <c r="N150" s="4"/>
       <c r="O150" s="4"/>
-      <c r="P150" s="4"/>
-      <c r="Q150" s="4"/>
-      <c r="R150" s="4"/>
-      <c r="S150" s="4"/>
     </row>
     <row r="151">
       <c r="A151" s="3"/>
@@ -5009,7 +4141,7 @@
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
       <c r="G151" s="3"/>
-      <c r="H151" s="3"/>
+      <c r="H151" s="4"/>
       <c r="I151" s="4"/>
       <c r="J151" s="4"/>
       <c r="K151" s="4"/>
@@ -5017,10 +4149,6 @@
       <c r="M151" s="4"/>
       <c r="N151" s="4"/>
       <c r="O151" s="4"/>
-      <c r="P151" s="4"/>
-      <c r="Q151" s="4"/>
-      <c r="R151" s="4"/>
-      <c r="S151" s="4"/>
     </row>
     <row r="152">
       <c r="A152" s="3"/>
@@ -5030,7 +4158,7 @@
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
       <c r="G152" s="3"/>
-      <c r="H152" s="3"/>
+      <c r="H152" s="4"/>
       <c r="I152" s="4"/>
       <c r="J152" s="4"/>
       <c r="K152" s="4"/>
@@ -5038,10 +4166,6 @@
       <c r="M152" s="4"/>
       <c r="N152" s="4"/>
       <c r="O152" s="4"/>
-      <c r="P152" s="4"/>
-      <c r="Q152" s="4"/>
-      <c r="R152" s="4"/>
-      <c r="S152" s="4"/>
     </row>
     <row r="153">
       <c r="A153" s="3"/>
@@ -5051,7 +4175,7 @@
       <c r="E153" s="3"/>
       <c r="F153" s="3"/>
       <c r="G153" s="3"/>
-      <c r="H153" s="3"/>
+      <c r="H153" s="4"/>
       <c r="I153" s="4"/>
       <c r="J153" s="4"/>
       <c r="K153" s="4"/>
@@ -5059,10 +4183,6 @@
       <c r="M153" s="4"/>
       <c r="N153" s="4"/>
       <c r="O153" s="4"/>
-      <c r="P153" s="4"/>
-      <c r="Q153" s="4"/>
-      <c r="R153" s="4"/>
-      <c r="S153" s="4"/>
     </row>
     <row r="154">
       <c r="A154" s="3"/>
@@ -5072,7 +4192,7 @@
       <c r="E154" s="3"/>
       <c r="F154" s="3"/>
       <c r="G154" s="3"/>
-      <c r="H154" s="3"/>
+      <c r="H154" s="4"/>
       <c r="I154" s="4"/>
       <c r="J154" s="4"/>
       <c r="K154" s="4"/>
@@ -5080,10 +4200,6 @@
       <c r="M154" s="4"/>
       <c r="N154" s="4"/>
       <c r="O154" s="4"/>
-      <c r="P154" s="4"/>
-      <c r="Q154" s="4"/>
-      <c r="R154" s="4"/>
-      <c r="S154" s="4"/>
     </row>
     <row r="155">
       <c r="A155" s="3"/>
@@ -5093,7 +4209,7 @@
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
       <c r="G155" s="3"/>
-      <c r="H155" s="3"/>
+      <c r="H155" s="4"/>
       <c r="I155" s="4"/>
       <c r="J155" s="4"/>
       <c r="K155" s="4"/>
@@ -5101,10 +4217,6 @@
       <c r="M155" s="4"/>
       <c r="N155" s="4"/>
       <c r="O155" s="4"/>
-      <c r="P155" s="4"/>
-      <c r="Q155" s="4"/>
-      <c r="R155" s="4"/>
-      <c r="S155" s="4"/>
     </row>
     <row r="156">
       <c r="A156" s="3"/>
@@ -5114,7 +4226,7 @@
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
       <c r="G156" s="3"/>
-      <c r="H156" s="3"/>
+      <c r="H156" s="4"/>
       <c r="I156" s="4"/>
       <c r="J156" s="4"/>
       <c r="K156" s="4"/>
@@ -5122,10 +4234,6 @@
       <c r="M156" s="4"/>
       <c r="N156" s="4"/>
       <c r="O156" s="4"/>
-      <c r="P156" s="4"/>
-      <c r="Q156" s="4"/>
-      <c r="R156" s="4"/>
-      <c r="S156" s="4"/>
     </row>
     <row r="157">
       <c r="A157" s="3"/>
@@ -5135,7 +4243,7 @@
       <c r="E157" s="3"/>
       <c r="F157" s="3"/>
       <c r="G157" s="3"/>
-      <c r="H157" s="3"/>
+      <c r="H157" s="4"/>
       <c r="I157" s="4"/>
       <c r="J157" s="4"/>
       <c r="K157" s="4"/>
@@ -5143,10 +4251,6 @@
       <c r="M157" s="4"/>
       <c r="N157" s="4"/>
       <c r="O157" s="4"/>
-      <c r="P157" s="4"/>
-      <c r="Q157" s="4"/>
-      <c r="R157" s="4"/>
-      <c r="S157" s="4"/>
     </row>
     <row r="158">
       <c r="A158" s="3"/>
@@ -5156,7 +4260,7 @@
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
       <c r="G158" s="3"/>
-      <c r="H158" s="3"/>
+      <c r="H158" s="4"/>
       <c r="I158" s="4"/>
       <c r="J158" s="4"/>
       <c r="K158" s="4"/>
@@ -5164,10 +4268,6 @@
       <c r="M158" s="4"/>
       <c r="N158" s="4"/>
       <c r="O158" s="4"/>
-      <c r="P158" s="4"/>
-      <c r="Q158" s="4"/>
-      <c r="R158" s="4"/>
-      <c r="S158" s="4"/>
     </row>
     <row r="159">
       <c r="A159" s="3"/>
@@ -5177,7 +4277,7 @@
       <c r="E159" s="3"/>
       <c r="F159" s="3"/>
       <c r="G159" s="3"/>
-      <c r="H159" s="3"/>
+      <c r="H159" s="4"/>
       <c r="I159" s="4"/>
       <c r="J159" s="4"/>
       <c r="K159" s="4"/>
@@ -5185,10 +4285,6 @@
       <c r="M159" s="4"/>
       <c r="N159" s="4"/>
       <c r="O159" s="4"/>
-      <c r="P159" s="4"/>
-      <c r="Q159" s="4"/>
-      <c r="R159" s="4"/>
-      <c r="S159" s="4"/>
     </row>
     <row r="160">
       <c r="A160" s="3"/>
@@ -5198,7 +4294,7 @@
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
       <c r="G160" s="3"/>
-      <c r="H160" s="3"/>
+      <c r="H160" s="4"/>
       <c r="I160" s="4"/>
       <c r="J160" s="4"/>
       <c r="K160" s="4"/>
@@ -5206,10 +4302,6 @@
       <c r="M160" s="4"/>
       <c r="N160" s="4"/>
       <c r="O160" s="4"/>
-      <c r="P160" s="4"/>
-      <c r="Q160" s="4"/>
-      <c r="R160" s="4"/>
-      <c r="S160" s="4"/>
     </row>
     <row r="161">
       <c r="A161" s="3"/>
@@ -5219,7 +4311,7 @@
       <c r="E161" s="3"/>
       <c r="F161" s="3"/>
       <c r="G161" s="3"/>
-      <c r="H161" s="3"/>
+      <c r="H161" s="4"/>
       <c r="I161" s="4"/>
       <c r="J161" s="4"/>
       <c r="K161" s="4"/>
@@ -5227,10 +4319,6 @@
       <c r="M161" s="4"/>
       <c r="N161" s="4"/>
       <c r="O161" s="4"/>
-      <c r="P161" s="4"/>
-      <c r="Q161" s="4"/>
-      <c r="R161" s="4"/>
-      <c r="S161" s="4"/>
     </row>
     <row r="162">
       <c r="A162" s="3"/>
@@ -5240,7 +4328,7 @@
       <c r="E162" s="3"/>
       <c r="F162" s="3"/>
       <c r="G162" s="3"/>
-      <c r="H162" s="3"/>
+      <c r="H162" s="4"/>
       <c r="I162" s="4"/>
       <c r="J162" s="4"/>
       <c r="K162" s="4"/>
@@ -5248,10 +4336,6 @@
       <c r="M162" s="4"/>
       <c r="N162" s="4"/>
       <c r="O162" s="4"/>
-      <c r="P162" s="4"/>
-      <c r="Q162" s="4"/>
-      <c r="R162" s="4"/>
-      <c r="S162" s="4"/>
     </row>
     <row r="163">
       <c r="A163" s="3"/>
@@ -5261,7 +4345,7 @@
       <c r="E163" s="3"/>
       <c r="F163" s="3"/>
       <c r="G163" s="3"/>
-      <c r="H163" s="3"/>
+      <c r="H163" s="4"/>
       <c r="I163" s="4"/>
       <c r="J163" s="4"/>
       <c r="K163" s="4"/>
@@ -5269,10 +4353,6 @@
       <c r="M163" s="4"/>
       <c r="N163" s="4"/>
       <c r="O163" s="4"/>
-      <c r="P163" s="4"/>
-      <c r="Q163" s="4"/>
-      <c r="R163" s="4"/>
-      <c r="S163" s="4"/>
     </row>
     <row r="164">
       <c r="A164" s="3"/>
@@ -5282,7 +4362,7 @@
       <c r="E164" s="3"/>
       <c r="F164" s="3"/>
       <c r="G164" s="3"/>
-      <c r="H164" s="3"/>
+      <c r="H164" s="4"/>
       <c r="I164" s="4"/>
       <c r="J164" s="4"/>
       <c r="K164" s="4"/>
@@ -5290,10 +4370,6 @@
       <c r="M164" s="4"/>
       <c r="N164" s="4"/>
       <c r="O164" s="4"/>
-      <c r="P164" s="4"/>
-      <c r="Q164" s="4"/>
-      <c r="R164" s="4"/>
-      <c r="S164" s="4"/>
     </row>
     <row r="165">
       <c r="A165" s="3"/>
@@ -5303,7 +4379,7 @@
       <c r="E165" s="3"/>
       <c r="F165" s="3"/>
       <c r="G165" s="3"/>
-      <c r="H165" s="3"/>
+      <c r="H165" s="4"/>
       <c r="I165" s="4"/>
       <c r="J165" s="4"/>
       <c r="K165" s="4"/>
@@ -5311,10 +4387,6 @@
       <c r="M165" s="4"/>
       <c r="N165" s="4"/>
       <c r="O165" s="4"/>
-      <c r="P165" s="4"/>
-      <c r="Q165" s="4"/>
-      <c r="R165" s="4"/>
-      <c r="S165" s="4"/>
     </row>
     <row r="166">
       <c r="A166" s="3"/>
@@ -5324,7 +4396,7 @@
       <c r="E166" s="3"/>
       <c r="F166" s="3"/>
       <c r="G166" s="3"/>
-      <c r="H166" s="3"/>
+      <c r="H166" s="4"/>
       <c r="I166" s="4"/>
       <c r="J166" s="4"/>
       <c r="K166" s="4"/>
@@ -5332,10 +4404,6 @@
       <c r="M166" s="4"/>
       <c r="N166" s="4"/>
       <c r="O166" s="4"/>
-      <c r="P166" s="4"/>
-      <c r="Q166" s="4"/>
-      <c r="R166" s="4"/>
-      <c r="S166" s="4"/>
     </row>
     <row r="167">
       <c r="A167" s="3"/>
@@ -5345,7 +4413,7 @@
       <c r="E167" s="3"/>
       <c r="F167" s="3"/>
       <c r="G167" s="3"/>
-      <c r="H167" s="3"/>
+      <c r="H167" s="4"/>
       <c r="I167" s="4"/>
       <c r="J167" s="4"/>
       <c r="K167" s="4"/>
@@ -5353,10 +4421,6 @@
       <c r="M167" s="4"/>
       <c r="N167" s="4"/>
       <c r="O167" s="4"/>
-      <c r="P167" s="4"/>
-      <c r="Q167" s="4"/>
-      <c r="R167" s="4"/>
-      <c r="S167" s="4"/>
     </row>
     <row r="168">
       <c r="A168" s="3"/>
@@ -5366,7 +4430,7 @@
       <c r="E168" s="3"/>
       <c r="F168" s="3"/>
       <c r="G168" s="3"/>
-      <c r="H168" s="3"/>
+      <c r="H168" s="4"/>
       <c r="I168" s="4"/>
       <c r="J168" s="4"/>
       <c r="K168" s="4"/>
@@ -5374,10 +4438,6 @@
       <c r="M168" s="4"/>
       <c r="N168" s="4"/>
       <c r="O168" s="4"/>
-      <c r="P168" s="4"/>
-      <c r="Q168" s="4"/>
-      <c r="R168" s="4"/>
-      <c r="S168" s="4"/>
     </row>
     <row r="169">
       <c r="A169" s="3"/>
@@ -5387,7 +4447,7 @@
       <c r="E169" s="3"/>
       <c r="F169" s="3"/>
       <c r="G169" s="3"/>
-      <c r="H169" s="3"/>
+      <c r="H169" s="4"/>
       <c r="I169" s="4"/>
       <c r="J169" s="4"/>
       <c r="K169" s="4"/>
@@ -5395,10 +4455,6 @@
       <c r="M169" s="4"/>
       <c r="N169" s="4"/>
       <c r="O169" s="4"/>
-      <c r="P169" s="4"/>
-      <c r="Q169" s="4"/>
-      <c r="R169" s="4"/>
-      <c r="S169" s="4"/>
     </row>
     <row r="170">
       <c r="A170" s="3"/>
@@ -5408,7 +4464,7 @@
       <c r="E170" s="3"/>
       <c r="F170" s="3"/>
       <c r="G170" s="3"/>
-      <c r="H170" s="3"/>
+      <c r="H170" s="4"/>
       <c r="I170" s="4"/>
       <c r="J170" s="4"/>
       <c r="K170" s="4"/>
@@ -5416,10 +4472,6 @@
       <c r="M170" s="4"/>
       <c r="N170" s="4"/>
       <c r="O170" s="4"/>
-      <c r="P170" s="4"/>
-      <c r="Q170" s="4"/>
-      <c r="R170" s="4"/>
-      <c r="S170" s="4"/>
     </row>
     <row r="171">
       <c r="A171" s="3"/>
@@ -5429,7 +4481,7 @@
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
       <c r="G171" s="3"/>
-      <c r="H171" s="3"/>
+      <c r="H171" s="4"/>
       <c r="I171" s="4"/>
       <c r="J171" s="4"/>
       <c r="K171" s="4"/>
@@ -5437,10 +4489,6 @@
       <c r="M171" s="4"/>
       <c r="N171" s="4"/>
       <c r="O171" s="4"/>
-      <c r="P171" s="4"/>
-      <c r="Q171" s="4"/>
-      <c r="R171" s="4"/>
-      <c r="S171" s="4"/>
     </row>
     <row r="172">
       <c r="A172" s="3"/>
@@ -5450,7 +4498,7 @@
       <c r="E172" s="3"/>
       <c r="F172" s="3"/>
       <c r="G172" s="3"/>
-      <c r="H172" s="3"/>
+      <c r="H172" s="4"/>
       <c r="I172" s="4"/>
       <c r="J172" s="4"/>
       <c r="K172" s="4"/>
@@ -5458,10 +4506,6 @@
       <c r="M172" s="4"/>
       <c r="N172" s="4"/>
       <c r="O172" s="4"/>
-      <c r="P172" s="4"/>
-      <c r="Q172" s="4"/>
-      <c r="R172" s="4"/>
-      <c r="S172" s="4"/>
     </row>
     <row r="173">
       <c r="A173" s="3"/>
@@ -5471,7 +4515,7 @@
       <c r="E173" s="3"/>
       <c r="F173" s="3"/>
       <c r="G173" s="3"/>
-      <c r="H173" s="3"/>
+      <c r="H173" s="4"/>
       <c r="I173" s="4"/>
       <c r="J173" s="4"/>
       <c r="K173" s="4"/>
@@ -5479,10 +4523,6 @@
       <c r="M173" s="4"/>
       <c r="N173" s="4"/>
       <c r="O173" s="4"/>
-      <c r="P173" s="4"/>
-      <c r="Q173" s="4"/>
-      <c r="R173" s="4"/>
-      <c r="S173" s="4"/>
     </row>
     <row r="174">
       <c r="A174" s="3"/>
@@ -5492,7 +4532,7 @@
       <c r="E174" s="3"/>
       <c r="F174" s="3"/>
       <c r="G174" s="3"/>
-      <c r="H174" s="3"/>
+      <c r="H174" s="4"/>
       <c r="I174" s="4"/>
       <c r="J174" s="4"/>
       <c r="K174" s="4"/>
@@ -5500,10 +4540,6 @@
       <c r="M174" s="4"/>
       <c r="N174" s="4"/>
       <c r="O174" s="4"/>
-      <c r="P174" s="4"/>
-      <c r="Q174" s="4"/>
-      <c r="R174" s="4"/>
-      <c r="S174" s="4"/>
     </row>
     <row r="175">
       <c r="A175" s="3"/>
@@ -5513,7 +4549,7 @@
       <c r="E175" s="3"/>
       <c r="F175" s="3"/>
       <c r="G175" s="3"/>
-      <c r="H175" s="3"/>
+      <c r="H175" s="4"/>
       <c r="I175" s="4"/>
       <c r="J175" s="4"/>
       <c r="K175" s="4"/>
@@ -5521,10 +4557,6 @@
       <c r="M175" s="4"/>
       <c r="N175" s="4"/>
       <c r="O175" s="4"/>
-      <c r="P175" s="4"/>
-      <c r="Q175" s="4"/>
-      <c r="R175" s="4"/>
-      <c r="S175" s="4"/>
     </row>
     <row r="176">
       <c r="A176" s="3"/>
@@ -5534,7 +4566,7 @@
       <c r="E176" s="3"/>
       <c r="F176" s="3"/>
       <c r="G176" s="3"/>
-      <c r="H176" s="3"/>
+      <c r="H176" s="4"/>
       <c r="I176" s="4"/>
       <c r="J176" s="4"/>
       <c r="K176" s="4"/>
@@ -5542,10 +4574,6 @@
       <c r="M176" s="4"/>
       <c r="N176" s="4"/>
       <c r="O176" s="4"/>
-      <c r="P176" s="4"/>
-      <c r="Q176" s="4"/>
-      <c r="R176" s="4"/>
-      <c r="S176" s="4"/>
     </row>
     <row r="177">
       <c r="A177" s="3"/>
@@ -5555,7 +4583,7 @@
       <c r="E177" s="3"/>
       <c r="F177" s="3"/>
       <c r="G177" s="3"/>
-      <c r="H177" s="3"/>
+      <c r="H177" s="4"/>
       <c r="I177" s="4"/>
       <c r="J177" s="4"/>
       <c r="K177" s="4"/>
@@ -5563,10 +4591,6 @@
       <c r="M177" s="4"/>
       <c r="N177" s="4"/>
       <c r="O177" s="4"/>
-      <c r="P177" s="4"/>
-      <c r="Q177" s="4"/>
-      <c r="R177" s="4"/>
-      <c r="S177" s="4"/>
     </row>
     <row r="178">
       <c r="A178" s="3"/>
@@ -5576,7 +4600,7 @@
       <c r="E178" s="3"/>
       <c r="F178" s="3"/>
       <c r="G178" s="3"/>
-      <c r="H178" s="3"/>
+      <c r="H178" s="4"/>
       <c r="I178" s="4"/>
       <c r="J178" s="4"/>
       <c r="K178" s="4"/>
@@ -5584,10 +4608,6 @@
       <c r="M178" s="4"/>
       <c r="N178" s="4"/>
       <c r="O178" s="4"/>
-      <c r="P178" s="4"/>
-      <c r="Q178" s="4"/>
-      <c r="R178" s="4"/>
-      <c r="S178" s="4"/>
     </row>
     <row r="179">
       <c r="A179" s="3"/>
@@ -5597,7 +4617,7 @@
       <c r="E179" s="3"/>
       <c r="F179" s="3"/>
       <c r="G179" s="3"/>
-      <c r="H179" s="3"/>
+      <c r="H179" s="4"/>
       <c r="I179" s="4"/>
       <c r="J179" s="4"/>
       <c r="K179" s="4"/>
@@ -5605,10 +4625,6 @@
       <c r="M179" s="4"/>
       <c r="N179" s="4"/>
       <c r="O179" s="4"/>
-      <c r="P179" s="4"/>
-      <c r="Q179" s="4"/>
-      <c r="R179" s="4"/>
-      <c r="S179" s="4"/>
     </row>
     <row r="180">
       <c r="A180" s="3"/>
@@ -5618,7 +4634,7 @@
       <c r="E180" s="3"/>
       <c r="F180" s="3"/>
       <c r="G180" s="3"/>
-      <c r="H180" s="3"/>
+      <c r="H180" s="4"/>
       <c r="I180" s="4"/>
       <c r="J180" s="4"/>
       <c r="K180" s="4"/>
@@ -5626,10 +4642,6 @@
       <c r="M180" s="4"/>
       <c r="N180" s="4"/>
       <c r="O180" s="4"/>
-      <c r="P180" s="4"/>
-      <c r="Q180" s="4"/>
-      <c r="R180" s="4"/>
-      <c r="S180" s="4"/>
     </row>
     <row r="181">
       <c r="A181" s="3"/>
@@ -5639,7 +4651,7 @@
       <c r="E181" s="3"/>
       <c r="F181" s="3"/>
       <c r="G181" s="3"/>
-      <c r="H181" s="3"/>
+      <c r="H181" s="4"/>
       <c r="I181" s="4"/>
       <c r="J181" s="4"/>
       <c r="K181" s="4"/>
@@ -5647,10 +4659,6 @@
       <c r="M181" s="4"/>
       <c r="N181" s="4"/>
       <c r="O181" s="4"/>
-      <c r="P181" s="4"/>
-      <c r="Q181" s="4"/>
-      <c r="R181" s="4"/>
-      <c r="S181" s="4"/>
     </row>
     <row r="182">
       <c r="A182" s="3"/>
@@ -5660,7 +4668,7 @@
       <c r="E182" s="3"/>
       <c r="F182" s="3"/>
       <c r="G182" s="3"/>
-      <c r="H182" s="3"/>
+      <c r="H182" s="4"/>
       <c r="I182" s="4"/>
       <c r="J182" s="4"/>
       <c r="K182" s="4"/>
@@ -5668,10 +4676,6 @@
       <c r="M182" s="4"/>
       <c r="N182" s="4"/>
       <c r="O182" s="4"/>
-      <c r="P182" s="4"/>
-      <c r="Q182" s="4"/>
-      <c r="R182" s="4"/>
-      <c r="S182" s="4"/>
     </row>
     <row r="183">
       <c r="A183" s="3"/>
@@ -5681,7 +4685,7 @@
       <c r="E183" s="3"/>
       <c r="F183" s="3"/>
       <c r="G183" s="3"/>
-      <c r="H183" s="3"/>
+      <c r="H183" s="4"/>
       <c r="I183" s="4"/>
       <c r="J183" s="4"/>
       <c r="K183" s="4"/>
@@ -5689,10 +4693,6 @@
       <c r="M183" s="4"/>
       <c r="N183" s="4"/>
       <c r="O183" s="4"/>
-      <c r="P183" s="4"/>
-      <c r="Q183" s="4"/>
-      <c r="R183" s="4"/>
-      <c r="S183" s="4"/>
     </row>
     <row r="184">
       <c r="A184" s="3"/>
@@ -5702,7 +4702,7 @@
       <c r="E184" s="3"/>
       <c r="F184" s="3"/>
       <c r="G184" s="3"/>
-      <c r="H184" s="3"/>
+      <c r="H184" s="4"/>
       <c r="I184" s="4"/>
       <c r="J184" s="4"/>
       <c r="K184" s="4"/>
@@ -5710,10 +4710,6 @@
       <c r="M184" s="4"/>
       <c r="N184" s="4"/>
       <c r="O184" s="4"/>
-      <c r="P184" s="4"/>
-      <c r="Q184" s="4"/>
-      <c r="R184" s="4"/>
-      <c r="S184" s="4"/>
     </row>
     <row r="185">
       <c r="A185" s="3"/>
@@ -5723,7 +4719,7 @@
       <c r="E185" s="3"/>
       <c r="F185" s="3"/>
       <c r="G185" s="3"/>
-      <c r="H185" s="3"/>
+      <c r="H185" s="4"/>
       <c r="I185" s="4"/>
       <c r="J185" s="4"/>
       <c r="K185" s="4"/>
@@ -5731,10 +4727,6 @@
       <c r="M185" s="4"/>
       <c r="N185" s="4"/>
       <c r="O185" s="4"/>
-      <c r="P185" s="4"/>
-      <c r="Q185" s="4"/>
-      <c r="R185" s="4"/>
-      <c r="S185" s="4"/>
     </row>
     <row r="186">
       <c r="A186" s="3"/>
@@ -5744,7 +4736,7 @@
       <c r="E186" s="3"/>
       <c r="F186" s="3"/>
       <c r="G186" s="3"/>
-      <c r="H186" s="3"/>
+      <c r="H186" s="4"/>
       <c r="I186" s="4"/>
       <c r="J186" s="4"/>
       <c r="K186" s="4"/>
@@ -5752,10 +4744,6 @@
       <c r="M186" s="4"/>
       <c r="N186" s="4"/>
       <c r="O186" s="4"/>
-      <c r="P186" s="4"/>
-      <c r="Q186" s="4"/>
-      <c r="R186" s="4"/>
-      <c r="S186" s="4"/>
     </row>
     <row r="187">
       <c r="A187" s="3"/>
@@ -5765,7 +4753,7 @@
       <c r="E187" s="3"/>
       <c r="F187" s="3"/>
       <c r="G187" s="3"/>
-      <c r="H187" s="3"/>
+      <c r="H187" s="4"/>
       <c r="I187" s="4"/>
       <c r="J187" s="4"/>
       <c r="K187" s="4"/>
@@ -5773,10 +4761,6 @@
       <c r="M187" s="4"/>
       <c r="N187" s="4"/>
       <c r="O187" s="4"/>
-      <c r="P187" s="4"/>
-      <c r="Q187" s="4"/>
-      <c r="R187" s="4"/>
-      <c r="S187" s="4"/>
     </row>
     <row r="188">
       <c r="A188" s="3"/>
@@ -5786,7 +4770,7 @@
       <c r="E188" s="3"/>
       <c r="F188" s="3"/>
       <c r="G188" s="3"/>
-      <c r="H188" s="3"/>
+      <c r="H188" s="4"/>
       <c r="I188" s="4"/>
       <c r="J188" s="4"/>
       <c r="K188" s="4"/>
@@ -5794,10 +4778,6 @@
       <c r="M188" s="4"/>
       <c r="N188" s="4"/>
       <c r="O188" s="4"/>
-      <c r="P188" s="4"/>
-      <c r="Q188" s="4"/>
-      <c r="R188" s="4"/>
-      <c r="S188" s="4"/>
     </row>
     <row r="189">
       <c r="A189" s="3"/>
@@ -5807,7 +4787,7 @@
       <c r="E189" s="3"/>
       <c r="F189" s="3"/>
       <c r="G189" s="3"/>
-      <c r="H189" s="3"/>
+      <c r="H189" s="4"/>
       <c r="I189" s="4"/>
       <c r="J189" s="4"/>
       <c r="K189" s="4"/>
@@ -5815,10 +4795,6 @@
       <c r="M189" s="4"/>
       <c r="N189" s="4"/>
       <c r="O189" s="4"/>
-      <c r="P189" s="4"/>
-      <c r="Q189" s="4"/>
-      <c r="R189" s="4"/>
-      <c r="S189" s="4"/>
     </row>
     <row r="190">
       <c r="A190" s="3"/>
@@ -5828,7 +4804,7 @@
       <c r="E190" s="3"/>
       <c r="F190" s="3"/>
       <c r="G190" s="3"/>
-      <c r="H190" s="3"/>
+      <c r="H190" s="4"/>
       <c r="I190" s="4"/>
       <c r="J190" s="4"/>
       <c r="K190" s="4"/>
@@ -5836,10 +4812,6 @@
       <c r="M190" s="4"/>
       <c r="N190" s="4"/>
       <c r="O190" s="4"/>
-      <c r="P190" s="4"/>
-      <c r="Q190" s="4"/>
-      <c r="R190" s="4"/>
-      <c r="S190" s="4"/>
     </row>
     <row r="191">
       <c r="A191" s="3"/>
@@ -5849,7 +4821,7 @@
       <c r="E191" s="3"/>
       <c r="F191" s="3"/>
       <c r="G191" s="3"/>
-      <c r="H191" s="3"/>
+      <c r="H191" s="4"/>
       <c r="I191" s="4"/>
       <c r="J191" s="4"/>
       <c r="K191" s="4"/>
@@ -5857,10 +4829,6 @@
       <c r="M191" s="4"/>
       <c r="N191" s="4"/>
       <c r="O191" s="4"/>
-      <c r="P191" s="4"/>
-      <c r="Q191" s="4"/>
-      <c r="R191" s="4"/>
-      <c r="S191" s="4"/>
     </row>
     <row r="192">
       <c r="A192" s="3"/>
@@ -5870,7 +4838,7 @@
       <c r="E192" s="3"/>
       <c r="F192" s="3"/>
       <c r="G192" s="3"/>
-      <c r="H192" s="3"/>
+      <c r="H192" s="4"/>
       <c r="I192" s="4"/>
       <c r="J192" s="4"/>
       <c r="K192" s="4"/>
@@ -5878,10 +4846,6 @@
       <c r="M192" s="4"/>
       <c r="N192" s="4"/>
       <c r="O192" s="4"/>
-      <c r="P192" s="4"/>
-      <c r="Q192" s="4"/>
-      <c r="R192" s="4"/>
-      <c r="S192" s="4"/>
     </row>
     <row r="193">
       <c r="A193" s="3"/>
@@ -5891,7 +4855,7 @@
       <c r="E193" s="3"/>
       <c r="F193" s="3"/>
       <c r="G193" s="3"/>
-      <c r="H193" s="3"/>
+      <c r="H193" s="4"/>
       <c r="I193" s="4"/>
       <c r="J193" s="4"/>
       <c r="K193" s="4"/>
@@ -5899,10 +4863,6 @@
       <c r="M193" s="4"/>
       <c r="N193" s="4"/>
       <c r="O193" s="4"/>
-      <c r="P193" s="4"/>
-      <c r="Q193" s="4"/>
-      <c r="R193" s="4"/>
-      <c r="S193" s="4"/>
     </row>
     <row r="194">
       <c r="A194" s="3"/>
@@ -5912,7 +4872,7 @@
       <c r="E194" s="3"/>
       <c r="F194" s="3"/>
       <c r="G194" s="3"/>
-      <c r="H194" s="3"/>
+      <c r="H194" s="4"/>
       <c r="I194" s="4"/>
       <c r="J194" s="4"/>
       <c r="K194" s="4"/>
@@ -5920,10 +4880,6 @@
       <c r="M194" s="4"/>
       <c r="N194" s="4"/>
       <c r="O194" s="4"/>
-      <c r="P194" s="4"/>
-      <c r="Q194" s="4"/>
-      <c r="R194" s="4"/>
-      <c r="S194" s="4"/>
     </row>
     <row r="195">
       <c r="A195" s="3"/>
@@ -5933,7 +4889,7 @@
       <c r="E195" s="3"/>
       <c r="F195" s="3"/>
       <c r="G195" s="3"/>
-      <c r="H195" s="3"/>
+      <c r="H195" s="4"/>
       <c r="I195" s="4"/>
       <c r="J195" s="4"/>
       <c r="K195" s="4"/>
@@ -5941,10 +4897,6 @@
       <c r="M195" s="4"/>
       <c r="N195" s="4"/>
       <c r="O195" s="4"/>
-      <c r="P195" s="4"/>
-      <c r="Q195" s="4"/>
-      <c r="R195" s="4"/>
-      <c r="S195" s="4"/>
     </row>
     <row r="196">
       <c r="A196" s="3"/>
@@ -5954,7 +4906,7 @@
       <c r="E196" s="3"/>
       <c r="F196" s="3"/>
       <c r="G196" s="3"/>
-      <c r="H196" s="3"/>
+      <c r="H196" s="4"/>
       <c r="I196" s="4"/>
       <c r="J196" s="4"/>
       <c r="K196" s="4"/>
@@ -5962,10 +4914,6 @@
       <c r="M196" s="4"/>
       <c r="N196" s="4"/>
       <c r="O196" s="4"/>
-      <c r="P196" s="4"/>
-      <c r="Q196" s="4"/>
-      <c r="R196" s="4"/>
-      <c r="S196" s="4"/>
     </row>
     <row r="197">
       <c r="A197" s="3"/>
@@ -5975,7 +4923,7 @@
       <c r="E197" s="3"/>
       <c r="F197" s="3"/>
       <c r="G197" s="3"/>
-      <c r="H197" s="3"/>
+      <c r="H197" s="4"/>
       <c r="I197" s="4"/>
       <c r="J197" s="4"/>
       <c r="K197" s="4"/>
@@ -5983,10 +4931,6 @@
       <c r="M197" s="4"/>
       <c r="N197" s="4"/>
       <c r="O197" s="4"/>
-      <c r="P197" s="4"/>
-      <c r="Q197" s="4"/>
-      <c r="R197" s="4"/>
-      <c r="S197" s="4"/>
     </row>
     <row r="198">
       <c r="A198" s="3"/>
@@ -5996,7 +4940,7 @@
       <c r="E198" s="3"/>
       <c r="F198" s="3"/>
       <c r="G198" s="3"/>
-      <c r="H198" s="3"/>
+      <c r="H198" s="4"/>
       <c r="I198" s="4"/>
       <c r="J198" s="4"/>
       <c r="K198" s="4"/>
@@ -6004,10 +4948,6 @@
       <c r="M198" s="4"/>
       <c r="N198" s="4"/>
       <c r="O198" s="4"/>
-      <c r="P198" s="4"/>
-      <c r="Q198" s="4"/>
-      <c r="R198" s="4"/>
-      <c r="S198" s="4"/>
     </row>
     <row r="199">
       <c r="A199" s="3"/>
@@ -6017,7 +4957,7 @@
       <c r="E199" s="3"/>
       <c r="F199" s="3"/>
       <c r="G199" s="3"/>
-      <c r="H199" s="3"/>
+      <c r="H199" s="4"/>
       <c r="I199" s="4"/>
       <c r="J199" s="4"/>
       <c r="K199" s="4"/>
@@ -6025,10 +4965,6 @@
       <c r="M199" s="4"/>
       <c r="N199" s="4"/>
       <c r="O199" s="4"/>
-      <c r="P199" s="4"/>
-      <c r="Q199" s="4"/>
-      <c r="R199" s="4"/>
-      <c r="S199" s="4"/>
     </row>
     <row r="200">
       <c r="A200" s="3"/>
@@ -6038,7 +4974,7 @@
       <c r="E200" s="3"/>
       <c r="F200" s="3"/>
       <c r="G200" s="3"/>
-      <c r="H200" s="3"/>
+      <c r="H200" s="4"/>
       <c r="I200" s="4"/>
       <c r="J200" s="4"/>
       <c r="K200" s="4"/>
@@ -6046,10 +4982,6 @@
       <c r="M200" s="4"/>
       <c r="N200" s="4"/>
       <c r="O200" s="4"/>
-      <c r="P200" s="4"/>
-      <c r="Q200" s="4"/>
-      <c r="R200" s="4"/>
-      <c r="S200" s="4"/>
     </row>
     <row r="201">
       <c r="A201" s="3"/>
@@ -6059,7 +4991,7 @@
       <c r="E201" s="3"/>
       <c r="F201" s="3"/>
       <c r="G201" s="3"/>
-      <c r="H201" s="3"/>
+      <c r="H201" s="4"/>
       <c r="I201" s="4"/>
       <c r="J201" s="4"/>
       <c r="K201" s="4"/>
@@ -6067,10 +4999,6 @@
       <c r="M201" s="4"/>
       <c r="N201" s="4"/>
       <c r="O201" s="4"/>
-      <c r="P201" s="4"/>
-      <c r="Q201" s="4"/>
-      <c r="R201" s="4"/>
-      <c r="S201" s="4"/>
     </row>
     <row r="202">
       <c r="A202" s="3"/>
@@ -6080,7 +5008,7 @@
       <c r="E202" s="3"/>
       <c r="F202" s="3"/>
       <c r="G202" s="3"/>
-      <c r="H202" s="3"/>
+      <c r="H202" s="4"/>
       <c r="I202" s="4"/>
       <c r="J202" s="4"/>
       <c r="K202" s="4"/>
@@ -6088,10 +5016,6 @@
       <c r="M202" s="4"/>
       <c r="N202" s="4"/>
       <c r="O202" s="4"/>
-      <c r="P202" s="4"/>
-      <c r="Q202" s="4"/>
-      <c r="R202" s="4"/>
-      <c r="S202" s="4"/>
     </row>
     <row r="203">
       <c r="A203" s="3"/>
@@ -6101,7 +5025,7 @@
       <c r="E203" s="3"/>
       <c r="F203" s="3"/>
       <c r="G203" s="3"/>
-      <c r="H203" s="3"/>
+      <c r="H203" s="4"/>
       <c r="I203" s="4"/>
       <c r="J203" s="4"/>
       <c r="K203" s="4"/>
@@ -6109,10 +5033,6 @@
       <c r="M203" s="4"/>
       <c r="N203" s="4"/>
       <c r="O203" s="4"/>
-      <c r="P203" s="4"/>
-      <c r="Q203" s="4"/>
-      <c r="R203" s="4"/>
-      <c r="S203" s="4"/>
     </row>
     <row r="204">
       <c r="A204" s="3"/>
@@ -6122,7 +5042,7 @@
       <c r="E204" s="3"/>
       <c r="F204" s="3"/>
       <c r="G204" s="3"/>
-      <c r="H204" s="3"/>
+      <c r="H204" s="4"/>
       <c r="I204" s="4"/>
       <c r="J204" s="4"/>
       <c r="K204" s="4"/>
@@ -6130,10 +5050,6 @@
       <c r="M204" s="4"/>
       <c r="N204" s="4"/>
       <c r="O204" s="4"/>
-      <c r="P204" s="4"/>
-      <c r="Q204" s="4"/>
-      <c r="R204" s="4"/>
-      <c r="S204" s="4"/>
     </row>
     <row r="205">
       <c r="A205" s="3"/>
@@ -6143,7 +5059,7 @@
       <c r="E205" s="3"/>
       <c r="F205" s="3"/>
       <c r="G205" s="3"/>
-      <c r="H205" s="3"/>
+      <c r="H205" s="4"/>
       <c r="I205" s="4"/>
       <c r="J205" s="4"/>
       <c r="K205" s="4"/>
@@ -6151,10 +5067,6 @@
       <c r="M205" s="4"/>
       <c r="N205" s="4"/>
       <c r="O205" s="4"/>
-      <c r="P205" s="4"/>
-      <c r="Q205" s="4"/>
-      <c r="R205" s="4"/>
-      <c r="S205" s="4"/>
     </row>
     <row r="206">
       <c r="A206" s="3"/>
@@ -6164,7 +5076,7 @@
       <c r="E206" s="3"/>
       <c r="F206" s="3"/>
       <c r="G206" s="3"/>
-      <c r="H206" s="3"/>
+      <c r="H206" s="4"/>
       <c r="I206" s="4"/>
       <c r="J206" s="4"/>
       <c r="K206" s="4"/>
@@ -6172,10 +5084,6 @@
       <c r="M206" s="4"/>
       <c r="N206" s="4"/>
       <c r="O206" s="4"/>
-      <c r="P206" s="4"/>
-      <c r="Q206" s="4"/>
-      <c r="R206" s="4"/>
-      <c r="S206" s="4"/>
     </row>
     <row r="207">
       <c r="A207" s="3"/>
@@ -6185,7 +5093,7 @@
       <c r="E207" s="3"/>
       <c r="F207" s="3"/>
       <c r="G207" s="3"/>
-      <c r="H207" s="3"/>
+      <c r="H207" s="4"/>
       <c r="I207" s="4"/>
       <c r="J207" s="4"/>
       <c r="K207" s="4"/>
@@ -6193,10 +5101,6 @@
       <c r="M207" s="4"/>
       <c r="N207" s="4"/>
       <c r="O207" s="4"/>
-      <c r="P207" s="4"/>
-      <c r="Q207" s="4"/>
-      <c r="R207" s="4"/>
-      <c r="S207" s="4"/>
     </row>
     <row r="208">
       <c r="A208" s="3"/>
@@ -6206,7 +5110,7 @@
       <c r="E208" s="3"/>
       <c r="F208" s="3"/>
       <c r="G208" s="3"/>
-      <c r="H208" s="3"/>
+      <c r="H208" s="4"/>
       <c r="I208" s="4"/>
       <c r="J208" s="4"/>
       <c r="K208" s="4"/>
@@ -6214,10 +5118,6 @@
       <c r="M208" s="4"/>
       <c r="N208" s="4"/>
       <c r="O208" s="4"/>
-      <c r="P208" s="4"/>
-      <c r="Q208" s="4"/>
-      <c r="R208" s="4"/>
-      <c r="S208" s="4"/>
     </row>
     <row r="209">
       <c r="A209" s="3"/>
@@ -6227,7 +5127,7 @@
       <c r="E209" s="3"/>
       <c r="F209" s="3"/>
       <c r="G209" s="3"/>
-      <c r="H209" s="3"/>
+      <c r="H209" s="4"/>
       <c r="I209" s="4"/>
       <c r="J209" s="4"/>
       <c r="K209" s="4"/>
@@ -6235,10 +5135,6 @@
       <c r="M209" s="4"/>
       <c r="N209" s="4"/>
       <c r="O209" s="4"/>
-      <c r="P209" s="4"/>
-      <c r="Q209" s="4"/>
-      <c r="R209" s="4"/>
-      <c r="S209" s="4"/>
     </row>
     <row r="210">
       <c r="A210" s="3"/>
@@ -6248,7 +5144,7 @@
       <c r="E210" s="3"/>
       <c r="F210" s="3"/>
       <c r="G210" s="3"/>
-      <c r="H210" s="3"/>
+      <c r="H210" s="4"/>
       <c r="I210" s="4"/>
       <c r="J210" s="4"/>
       <c r="K210" s="4"/>
@@ -6256,10 +5152,6 @@
       <c r="M210" s="4"/>
       <c r="N210" s="4"/>
       <c r="O210" s="4"/>
-      <c r="P210" s="4"/>
-      <c r="Q210" s="4"/>
-      <c r="R210" s="4"/>
-      <c r="S210" s="4"/>
     </row>
     <row r="211">
       <c r="A211" s="3"/>
@@ -6269,7 +5161,7 @@
       <c r="E211" s="3"/>
       <c r="F211" s="3"/>
       <c r="G211" s="3"/>
-      <c r="H211" s="3"/>
+      <c r="H211" s="4"/>
       <c r="I211" s="4"/>
       <c r="J211" s="4"/>
       <c r="K211" s="4"/>
@@ -6277,10 +5169,6 @@
       <c r="M211" s="4"/>
       <c r="N211" s="4"/>
       <c r="O211" s="4"/>
-      <c r="P211" s="4"/>
-      <c r="Q211" s="4"/>
-      <c r="R211" s="4"/>
-      <c r="S211" s="4"/>
     </row>
     <row r="212">
       <c r="A212" s="3"/>
@@ -6290,7 +5178,7 @@
       <c r="E212" s="3"/>
       <c r="F212" s="3"/>
       <c r="G212" s="3"/>
-      <c r="H212" s="3"/>
+      <c r="H212" s="4"/>
       <c r="I212" s="4"/>
       <c r="J212" s="4"/>
       <c r="K212" s="4"/>
@@ -6298,10 +5186,6 @@
       <c r="M212" s="4"/>
       <c r="N212" s="4"/>
       <c r="O212" s="4"/>
-      <c r="P212" s="4"/>
-      <c r="Q212" s="4"/>
-      <c r="R212" s="4"/>
-      <c r="S212" s="4"/>
     </row>
     <row r="213">
       <c r="A213" s="3"/>
@@ -6311,7 +5195,7 @@
       <c r="E213" s="3"/>
       <c r="F213" s="3"/>
       <c r="G213" s="3"/>
-      <c r="H213" s="3"/>
+      <c r="H213" s="4"/>
       <c r="I213" s="4"/>
       <c r="J213" s="4"/>
       <c r="K213" s="4"/>
@@ -6319,10 +5203,6 @@
       <c r="M213" s="4"/>
       <c r="N213" s="4"/>
       <c r="O213" s="4"/>
-      <c r="P213" s="4"/>
-      <c r="Q213" s="4"/>
-      <c r="R213" s="4"/>
-      <c r="S213" s="4"/>
     </row>
     <row r="214">
       <c r="A214" s="3"/>
@@ -6332,7 +5212,7 @@
       <c r="E214" s="3"/>
       <c r="F214" s="3"/>
       <c r="G214" s="3"/>
-      <c r="H214" s="3"/>
+      <c r="H214" s="4"/>
       <c r="I214" s="4"/>
       <c r="J214" s="4"/>
       <c r="K214" s="4"/>
@@ -6340,23 +5220,22 @@
       <c r="M214" s="4"/>
       <c r="N214" s="4"/>
       <c r="O214" s="4"/>
-      <c r="P214" s="4"/>
-      <c r="Q214" s="4"/>
-      <c r="R214" s="4"/>
-      <c r="S214" s="4"/>
     </row>
   </sheetData>
-  <dataValidations count="10">
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K214">
+  <dataValidations count="8">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J214">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O214">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N214">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H214">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I214">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J214">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K214">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L214">
@@ -6365,16 +5244,7 @@
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M214">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N214">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P214">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q214">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S214">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O214">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -6383,18 +5253,12 @@
   <legacyDrawing r:id="rIdvml"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'Listas'!$A$2:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H214</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>'Listas'!$B$2:$B$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>R2:R214</xm:sqref>
+          <xm:sqref>G2:G214</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6414,10 +5278,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>9</v>
@@ -6425,35 +5289,35 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>0.955</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -6481,13 +5345,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
@@ -6498,7 +5362,7 @@
         <v>0.62</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3">
@@ -6509,7 +5373,7 @@
         <v>0.825</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4">
@@ -6517,7 +5381,7 @@
         <v>0.955</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Modelos/Entrada_DM.xlsx
+++ b/Modelos/Entrada_DM.xlsx
@@ -100,7 +100,7 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Sim = entra no DM médio do componente; Não = fica de fora</t>
+          <t xml:space="preserve">Sim = VBC com os parâmetros d, y e t; Não = VBC sem os parâmetros</t>
         </r>
       </text>
     </comment>
@@ -205,7 +205,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <si>
     <t xml:space="preserve">Planilha de entrada para R/DM-Calculo_Perdas_Ganhos.R</t>
   </si>
@@ -508,6 +508,9 @@
   </si>
   <si>
     <t xml:space="preserve">alta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sim = VBC com os parâmetros d, y e t; Não = VBC sem os parâmetros</t>
   </si>
 </sst>
 </file>
@@ -1021,7 +1024,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
         <v>1</v>
